--- a/results/cluster_ga/UAVs7_GRID13/revenue/UAVs7_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs7_GRID13/revenue/UAVs7_GRID13_Greedy.xlsx
@@ -662,25 +662,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.63205152465825</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.37484492338629</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.18682023182991</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.06841455590436</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.12941545456005</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.53256469749602</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.72490704085293</v>
+        <v>33.49316347814121</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.16955034796628</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.00324664840058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.0441247492582</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.07489606688205</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.40833589317389</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.25368679140186</v>
       </c>
     </row>
   </sheetData>
@@ -744,25 +744,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.55846716417438</v>
-      </c>
-      <c r="C2" t="n">
-        <v>55.99589670985675</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.00814425140859</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.15359554932625</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.0633060627406</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.69413211713304</v>
-      </c>
-      <c r="H2" t="n">
-        <v>18.19850664363427</v>
+        <v>34.56820737059347</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.10792165384182</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.02515140837805</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.14084825282851</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.20936858227284</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.21903444171383</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.74348546828483</v>
       </c>
     </row>
   </sheetData>
@@ -826,25 +826,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.65352850987279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.86186712971237</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.86338803339176</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.08403478662538</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.34017633594805</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.6531299079088</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.72030370995757</v>
+        <v>24.99557704925561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.26313587799041</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.36042600766485</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.61109375607475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.83603679513557</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.56486894498159</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.8550035109799</v>
       </c>
     </row>
   </sheetData>
@@ -908,25 +908,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.35772847919297</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.41299322249944</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.85159737035102</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.90400471041932</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.42898493352934</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.66728291297623</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.32810156556492</v>
+        <v>32.65221851107844</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.61020267496868</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.02327484005878</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.09716268026227</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.20540734089483</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.23015867634845</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.01724882192416</v>
       </c>
     </row>
   </sheetData>
@@ -990,25 +990,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.32574303265347</v>
-      </c>
-      <c r="C2" t="n">
-        <v>55.14978217595728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.92863058640555</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.02333060820258</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.81418726744086</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.58965510409415</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.51875694836473</v>
+        <v>37.75797389267687</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.64922565797134</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.37426915781388</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.21400761366209</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.5840494221057</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.93869325061234</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.03279064657352</v>
       </c>
     </row>
   </sheetData>
@@ -1072,25 +1072,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.49820278501539</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.79677516231775</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.3637963983566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>53.44978621076598</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.70076172211241</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.06600546164188</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.5356355936127</v>
+        <v>30.94654486530823</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.50389553505415</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.30521886361199</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.44456765899604</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.34247705327588</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.76181171966364</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.30205896415264</v>
       </c>
     </row>
   </sheetData>
@@ -1154,25 +1154,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.33819973188575</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.19889669220908</v>
-      </c>
-      <c r="D2" t="n">
-        <v>60.16876028505254</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.61257821356261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.08555128613128</v>
-      </c>
-      <c r="G2" t="n">
-        <v>51.03713061631084</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.44046725989454</v>
+        <v>31.40154191645078</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.42350883650443</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.43397131528192</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.08083984390266</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.11879720866835</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51.27352436644643</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.39303418662271</v>
       </c>
     </row>
   </sheetData>
@@ -1236,25 +1236,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.47638753507206</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.487918085217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.55493186552735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.29356241119889</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.35074878386613</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.12463192116697</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.5345786532196</v>
+        <v>36.28512575704318</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.44554588085013</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.70197992308049</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.53922567771456</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.25303620554306</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.64533939016857</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.75764719446076</v>
       </c>
     </row>
   </sheetData>
@@ -1318,25 +1318,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.43386501794082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>61.14537586970005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.28503082395151</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.7557543659713</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.74225274497701</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.73569506328632</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.17517200891452</v>
+        <v>32.66502562712351</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.25406158954291</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.03023590166987</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.17848484366404</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.84133339875297</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.23229250035487</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.04019544612726</v>
       </c>
     </row>
   </sheetData>
@@ -1400,25 +1400,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.37190567847947</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.2505225042814</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.79878716154735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.60037692117619</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.72702952640763</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.50288717618901</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.49954104786955</v>
+        <v>35.75725879759379</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.09635926157782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.35632031381564</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.0775231683194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51.94767517624697</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.1256362384791</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.89598794305441</v>
       </c>
     </row>
   </sheetData>
@@ -1482,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.51489564062692</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.233197733391</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.40364865771132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.75088191578016</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.05561095924922</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.60476643542334</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.10370837253542</v>
+        <v>33.66000216663236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.82436175908649</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50.09787100890821</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.52138436321085</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.08464849462987</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.44212054721675</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.55059753617432</v>
       </c>
     </row>
   </sheetData>
@@ -1564,25 +1564,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.23591070928729</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.6710884021067</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.28758634087252</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.31082645481209</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.6602280469537</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.49262317631866</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.74997981616195</v>
+        <v>32.99488151243053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.34143922731437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.14241445828831</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.23913300743651</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.05592779681345</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.42744255084511</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.60714208993293</v>
       </c>
     </row>
   </sheetData>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.87655929498847</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.89294165340446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.48671683357667</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.52309525084165</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.79129560408951</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.71000687188918</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.49482396652641</v>
+        <v>33.76041880280954</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.41826327184367</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.62777213117542</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.09365530760045</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.73877186089307</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.89781520933777</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.24806911328352</v>
       </c>
     </row>
   </sheetData>
@@ -1728,25 +1728,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.85922855192027</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.42028597783933</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.14120409519252</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.39265324800935</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.04990597460455</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.700743496929</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.23074280952044</v>
+        <v>39.68873912151668</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.93080074632267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.17912659533258</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.31984511859839</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.87954110491869</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.68951169245769</v>
+      </c>
+      <c r="H2" t="n">
+        <v>55.23403394598958</v>
       </c>
     </row>
   </sheetData>
@@ -1810,25 +1810,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.3857502922106</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.59303129120892</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.82009617185185</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.73789746478221</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.36292583477196</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.90835554783121</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.42099578430878</v>
+        <v>33.68681324604061</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.84535132125564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.74335743221831</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.4390497192883</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.62517139184004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.59651827243441</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.97842602129022</v>
       </c>
     </row>
   </sheetData>
@@ -1892,25 +1892,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.28693036457507</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.36471060958372</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.90968898693848</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.33500825571257</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.72577143803467</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.65029120459844</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.98905570495511</v>
+        <v>23.18280602042724</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.79910008523032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.21127630949078</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.7153429563324</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.73428320766959</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.11881541499976</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.94412919560637</v>
       </c>
     </row>
   </sheetData>
@@ -1974,25 +1974,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.33203041126703</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.35088000827675</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.98275527079406</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.21126630292383</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.72318019002714</v>
-      </c>
-      <c r="G2" t="n">
-        <v>21.38676465892928</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.30057698339171</v>
+        <v>26.61142828083305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.69335833467314</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.27382129260261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.92869692254151</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.78005036482149</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.55462409147765</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.28143685068244</v>
       </c>
     </row>
   </sheetData>
@@ -2056,25 +2056,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.07014390876179</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.11527610115097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.93891313181258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.47150495057345</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.78792142092315</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.07757511344403</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.28011522992317</v>
+        <v>24.99047642642999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.7881374120086</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.69940783739025</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.45864908255719</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.63821227520688</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.76891347194458</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.44334979580223</v>
       </c>
     </row>
   </sheetData>
@@ -2138,25 +2138,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.42975389268659</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.61891951390823</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.54550063368705</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.94491942961226</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.59688531978826</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.73024909003352</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.67302505047984</v>
+        <v>32.8087152586062</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.1145396638004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.72694712426041</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.06032273339167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.14127795088856</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.52805418314847</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.43852161436975</v>
       </c>
     </row>
   </sheetData>
@@ -2220,25 +2220,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.38511705777329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.67374897417872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.03400545080918</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.29830788444188</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.8899774706451</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.82065513374513</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.09789379574434</v>
+        <v>27.44701762445519</v>
+      </c>
+      <c r="C2" t="n">
+        <v>59.13367754859861</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.60987122367932</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.57807115085908</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.80542911159171</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.33846407713966</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.00841783203556</v>
       </c>
     </row>
   </sheetData>
@@ -2302,25 +2302,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.87303951501348</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.90960893904072</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.25851619898124</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.29485187532733</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.89665648748779</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.10338476285129</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19.87014141265085</v>
+        <v>32.84320438579207</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.91346543984289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.11943650665672</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.68371143694154</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.99659713062576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.83764545059708</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50.58381301128932</v>
       </c>
     </row>
   </sheetData>
@@ -2384,25 +2384,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.71742146813337</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.68091540297531</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.76338720979403</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.94304137357994</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.85663768387886</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.57460379996037</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21.36340223839778</v>
+        <v>36.57377544327483</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.78557947567612</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.70344175865215</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.4195101435789</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.180241829317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.53204272657621</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.19522803973321</v>
       </c>
     </row>
   </sheetData>
@@ -2466,25 +2466,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.30581752156741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.42358188600002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.93754150558362</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.72885333280365</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.2732966989423</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.37914804609035</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.07167758945573</v>
+        <v>31.56036746762787</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.21217528619853</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.03905718322945</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.57025410970996</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.11506381611894</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.6337882149272</v>
+      </c>
+      <c r="H2" t="n">
+        <v>54.15935637108271</v>
       </c>
     </row>
   </sheetData>
@@ -2548,25 +2548,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.63324631999546</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.95067286164089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.26678357860182</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.88514986352091</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.62460895007396</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.92365697934633</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.4978007962014</v>
+        <v>35.88018831287886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.92615359828353</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.50384606041656</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.33160805731794</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.92594042285835</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.97247982646076</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.77203882577895</v>
       </c>
     </row>
   </sheetData>
@@ -2630,25 +2630,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.94025204089984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.04243895974921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.60362818006219</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.10638626791467</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.39883456999245</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.7686331753185</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.58441707449979</v>
+        <v>29.94519703122737</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.36181801235553</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.27302454303494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.88901383788298</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.32576215297041</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.35511222270566</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.80028096141713</v>
       </c>
     </row>
   </sheetData>
@@ -2712,25 +2712,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.47046371636678</v>
-      </c>
-      <c r="C2" t="n">
-        <v>418.1037609967428</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.1818320989556</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.18879218875733</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.92521584453448</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.70655925289727</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.93780088934479</v>
+        <v>35.42676443936986</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.08003389099738</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.43252670259811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.77205603841758</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.57953280067174</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.10602511242742</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.21137123575414</v>
       </c>
     </row>
   </sheetData>
@@ -2794,25 +2794,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.44742771204137</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.01640354232659</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.52656179664267</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.97496141527687</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.55812714138487</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.2107509300225</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.34423468305063</v>
+        <v>32.44550058681877</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.73724469901772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.60177243406261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.23093662515199</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.57172378393574</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.73903574153434</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.78749842788159</v>
       </c>
     </row>
   </sheetData>
@@ -2876,25 +2876,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.52419448547439</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.81685598091431</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.1440625095505</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.84137697238734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.28984844684775</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.53921823989414</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.70659821232768</v>
+        <v>42.34848832243589</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.35392377530188</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.4553651995087</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.68558653283705</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.7118088480637</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.32573956555103</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.5136569847774</v>
       </c>
     </row>
   </sheetData>
@@ -2958,25 +2958,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.48692876147295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.76566827314143</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.79658930718547</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.2679976655129</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.45725463186614</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.30241296136922</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.81092254072458</v>
+        <v>30.46418881861136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.9618106986708</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.94307313255707</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55.74689497950804</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.23827972468774</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.86481932224477</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.91048611871987</v>
       </c>
     </row>
   </sheetData>
@@ -3040,25 +3040,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.8886225999611</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.17536072722459</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.30518717903706</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.60376506578295</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14.49232267187484</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.74827941556853</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.57516016853866</v>
+        <v>33.44736248460281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.91243554573059</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.75852108874931</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.03887318166917</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.74908047071024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.21432594465035</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.81146696557609</v>
       </c>
     </row>
   </sheetData>
@@ -3122,25 +3122,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.06529036121076</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.28010062049633</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.44578157099398</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.89240347308899</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.1745281787974</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.08726461546164</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.82074309298295</v>
+        <v>29.71652785387895</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.66163599744782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.15057538760021</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.09584014734255</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.11587295220671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.3415643455934</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.67487610133212</v>
       </c>
     </row>
   </sheetData>
@@ -3204,25 +3204,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.63421350376956</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.46657097209658</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.61527603929184</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.26708196254355</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.80402645586689</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.49140235067738</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22.43518079265296</v>
+        <v>26.76067390448774</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.50541275006556</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.91564177728886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.71940675109974</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.55275003688585</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.22441567057713</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.55739788444998</v>
       </c>
     </row>
   </sheetData>
@@ -3286,25 +3286,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.39172265415404</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.15947874101794</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.76979988768174</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.03792314985046</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.20837936702364</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.87453088026372</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.9399317584744</v>
+        <v>36.16867194910421</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.34473355999246</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.4257768015658</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.37134928136449</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.25887130877595</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.50688682094431</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.98637344530344</v>
       </c>
     </row>
   </sheetData>
@@ -3368,25 +3368,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.64625441013581</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.580164133024</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.52885645622592</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.32887685017041</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.16886509787302</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.10992344643709</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.71193914672534</v>
+        <v>32.49191129769017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.16215672424661</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.87373162139335</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.13334938682517</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.21901272021596</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.81444421182979</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.19627354968259</v>
       </c>
     </row>
   </sheetData>
@@ -3450,25 +3450,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.22629874625041</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.15563865547437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.38185129246671</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.30717254810573</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.89337500081463</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.19304577060946</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22.47370693012722</v>
+        <v>27.04429449003088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.89639252062479</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.67829974020541</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.9089418017108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.58185414574233</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.26474932836737</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.23881534424982</v>
       </c>
     </row>
   </sheetData>
@@ -3532,25 +3532,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.9283434075952</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.65813959401937</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.23887852838523</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.33984998039641</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.45993383667376</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.53954041066701</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.16005321307059</v>
+        <v>36.08399621871876</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.15463446923637</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.9538490121719</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.6948064031334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.12500853317962</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.22930501348031</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.12328506939843</v>
       </c>
     </row>
   </sheetData>
@@ -3614,25 +3614,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.18564031383464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.0362072450171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.7348525741151</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.13651606297321</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.15142398391978</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.66468546745087</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50.41544013445991</v>
+        <v>37.98904976924324</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60.82570494383436</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.30455202974495</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.31335512244809</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.9907034914125</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.9398103610289</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.61980035556478</v>
       </c>
     </row>
   </sheetData>
@@ -3696,25 +3696,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.98037992051319</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.36600174682473</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.15664877586217</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.72981973128388</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.43209179689441</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.132462700378</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.70020201913787</v>
+        <v>32.27332494054795</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.13449417775379</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.61064097551338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.12314802099523</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.53716054223912</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.48024064690669</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.57194607760158</v>
       </c>
     </row>
   </sheetData>
@@ -3778,25 +3778,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.52249543850128</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.55907064388656</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.69900424194185</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.75643425062425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.97776630982062</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.94438009543743</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.2703276752141</v>
+        <v>31.28542778794264</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.32382735781999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.87498068142947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.25275153854982</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.83969105366361</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.74987222614377</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.37175817139696</v>
       </c>
     </row>
   </sheetData>
@@ -3860,25 +3860,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.13636105315932</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.64893118330707</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.64023719181719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.56250629441458</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.28360868999574</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.06858393161917</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20.1234636037905</v>
+        <v>27.11293870703903</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.4500346946718</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.85686194585143</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.72920942772467</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.10630255483353</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.42177538788305</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.00127127302809</v>
       </c>
     </row>
   </sheetData>
@@ -3942,25 +3942,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.96365322404692</v>
-      </c>
-      <c r="C2" t="n">
-        <v>55.11434390360952</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.35344043868754</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.61328911405506</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.5145865025382</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.14445338358505</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.87523622216167</v>
+        <v>32.83980740826963</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.66092558647139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.95950509842039</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.4907140683771</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.48699465711965</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.80959147493601</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.44602024095955</v>
       </c>
     </row>
   </sheetData>
@@ -4024,25 +4024,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.42889361318868</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.36402004696065</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.07264803811571</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.81197320695674</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.29481932883876</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.32697855627242</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.5810342269115</v>
+        <v>28.7367217357647</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.74714052396618</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.36213474288613</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.10611604438598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.95232961330869</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.24732683711839</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.76081245603521</v>
       </c>
     </row>
   </sheetData>
@@ -4106,25 +4106,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.24839360512932</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.29766502847109</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.89695187845039</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.03051905426882</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.79473407641351</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.26705944745839</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.97688584699735</v>
+        <v>29.75599568297746</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.37176424489282</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.8557654043752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.59036497936273</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.371443815327</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.67128913433771</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.93874212908572</v>
       </c>
     </row>
   </sheetData>
@@ -4188,25 +4188,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.87002806953032</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.15656636048934</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.69112143894138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.50245627257492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.67538750163308</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.27464949837681</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.92632169500834</v>
+        <v>33.71274217089696</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.03993051278976</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.39215865049666</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.120991668061</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.83820332417326</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.80899921680975</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.35919575997794</v>
       </c>
     </row>
   </sheetData>
@@ -4270,25 +4270,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.16974969434855</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.52404958946247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.5575271008604</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.04695624563906</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.90003974179495</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.72317104227128</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.0983545859844</v>
+        <v>38.01895894384506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.47215629684388</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.50280164657505</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.9323706062006</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.76573947880872</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.70237893916728</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.06338327153911</v>
       </c>
     </row>
   </sheetData>
@@ -4352,25 +4352,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.2666749444554</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.61970502780936</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.74733577667955</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.95033662784154</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.47597164730654</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.36924922115021</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.75983250602031</v>
+        <v>36.72979830775966</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.19696735897437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.13383445851248</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.10544837133139</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.74798735594099</v>
+      </c>
+      <c r="G2" t="n">
+        <v>53.41740470961474</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.78931598598503</v>
       </c>
     </row>
   </sheetData>
@@ -4434,25 +4434,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.73332659948489</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.19380281168602</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.49903859108743</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.94891703927907</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.24701265504738</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.84405371816386</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.92450442653738</v>
+        <v>26.18958066071286</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.67752392435209</v>
+      </c>
+      <c r="D2" t="n">
+        <v>67.9102041468757</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.93239454297988</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.50326278935581</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.3086165042091</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.82132633499743</v>
       </c>
     </row>
   </sheetData>
@@ -4516,25 +4516,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.7927270156801</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.6135437549589</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.00451653207949</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.45215296245293</v>
-      </c>
-      <c r="F2" t="n">
-        <v>59.03809833089034</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.68529655391947</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.41815556831904</v>
+        <v>39.66845895856049</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.42568541447017</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.97444277937374</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.79868449520448</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.74014995028577</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.54832309065181</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.90774932519867</v>
       </c>
     </row>
   </sheetData>
@@ -4598,25 +4598,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.40159566953372</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.52357248969668</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.82459329815786</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.27211980902019</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.88092019057527</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.040588297281</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.07422489069715</v>
+        <v>32.24390110365069</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.12290476600373</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.72032494134098</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.07109800041552</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.48878717369437</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.19577291369733</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.71543710191004</v>
       </c>
     </row>
   </sheetData>
@@ -4680,25 +4680,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.34644259684796</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.67273087204463</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.72005777507387</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.30720034385568</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.40601172237012</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.16407229132757</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.76764649801246</v>
+        <v>33.98640359996705</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.04370890006045</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.72560593586359</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.66707818686154</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.16601761999623</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.95015030210817</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.01583449887566</v>
       </c>
     </row>
   </sheetData>
@@ -4762,25 +4762,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.25538660831058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.45708737962317</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.72324548946462</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.89675138504274</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.92250082061425</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.00634109308566</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.26311708982062</v>
+        <v>31.65459737404945</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.67803048959732</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.52065786905036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.8706104815944</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.45034781158294</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.91613177166994</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.21788415174737</v>
       </c>
     </row>
   </sheetData>
@@ -4844,25 +4844,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.01141982837983</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.70080736901461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.36946416026095</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.66256345649925</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.41834653947922</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.54048212652906</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.48606219414103</v>
+        <v>31.42715143054543</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.54375008966307</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.9563479001546</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.65083351141363</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.12795829473637</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.45106595153446</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.16847607863347</v>
       </c>
     </row>
   </sheetData>
@@ -4926,25 +4926,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.63880613046594</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.0647773625105</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.10387400453308</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.24578526134822</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.51759498957572</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.95585501217595</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.39196889669363</v>
+        <v>34.62575074595264</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.05854893677877</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.83897618043776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.81053348329446</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.3815347467009</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.46632498505593</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.68743867310353</v>
       </c>
     </row>
   </sheetData>
@@ -5008,25 +5008,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.97223486496113</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.68273166794988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.4805817098793</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.59315147487158</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.91335140021446</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.46236589963672</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.06811211079042</v>
+        <v>26.78264668713368</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.76370151542581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.53289586897127</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.77633079250038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.53204440241331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.34813742367628</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.59332475748324</v>
       </c>
     </row>
   </sheetData>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.63393458126856</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.37687675996475</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.60016137923631</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.60505856562857</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.0570096337125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.56737696951649</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.80215043727408</v>
+        <v>32.64822212772071</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.34746616591921</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.32496569300484</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.98188806612709</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.83076654533674</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.73697317817258</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.35046340577334</v>
       </c>
     </row>
   </sheetData>
@@ -5172,25 +5172,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.42912151840834</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.59477578789639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.04995030170453</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.66206870068133</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.88110108317992</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.26161863650644</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.15932991115667</v>
+        <v>23.1456164369385</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.6178000817217</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.87463932659583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>54.04763716243029</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.59887659837519</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.09380666744162</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.3535900372711</v>
       </c>
     </row>
   </sheetData>
@@ -5254,25 +5254,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.36976426870012</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.44753599809535</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.6664729993435</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.74511766128385</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.28122945297642</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.03025015767474</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.56547377159893</v>
+        <v>33.90053204824778</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.24147509551833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.46086114181126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.89034493255706</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.90495601341645</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.06070673874726</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.61695075561205</v>
       </c>
     </row>
   </sheetData>
@@ -5336,25 +5336,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.88505880166776</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.07917752198883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.96991666687459</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.56181013306054</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.44558330610935</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.75266056247104</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.15927100589556</v>
+        <v>31.85458104287871</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.09796428436132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.3286813012528</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.25329680231191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.58955709396824</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.73568809377061</v>
+      </c>
+      <c r="H2" t="n">
+        <v>47.92760279870074</v>
       </c>
     </row>
   </sheetData>
@@ -5418,25 +5418,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.27863860497021</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.49890530567244</v>
-      </c>
-      <c r="D2" t="n">
-        <v>60.42783459623485</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.13853971422455</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.25776606223464</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.99450478002546</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.77520127559863</v>
+        <v>25.11096945145049</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.14104996533543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.09672952094744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.83624841352363</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.04363530383862</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.72536596330685</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.44190310424868</v>
       </c>
     </row>
   </sheetData>
@@ -5500,25 +5500,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52237886376295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.66971967592465</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.32227868157177</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.37480544793952</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.67579164853573</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.25848028418283</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.01212520956322</v>
+        <v>31.09563768296477</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.60108180124919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.31025793000998</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.90247921428565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.99853681175965</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.81102850126589</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.28480642203485</v>
       </c>
     </row>
   </sheetData>
@@ -5582,25 +5582,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.81286575973358</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.98305803361091</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.94756054939137</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.74918343286964</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.24028880796675</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.91236705806935</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.05583335038447</v>
+        <v>24.21182214208956</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.1233390801701</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.39757140520855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.56459013675608</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.55408998894706</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.51192442586067</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.8046236837953</v>
       </c>
     </row>
   </sheetData>
@@ -5664,25 +5664,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.02534620490686</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.1094406472596</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.41332501210378</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.32289302357195</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.1108650028359</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.13262929554588</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.94827031568052</v>
+        <v>36.02425605149507</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.58175086729833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57.91556407368697</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.3070049292194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.24286249259266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.67667674553378</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.26827994294196</v>
       </c>
     </row>
   </sheetData>
@@ -5746,25 +5746,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.57957073942679</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.57660171682287</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.16106859437</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.0560309953406</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.19250232279349</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.17355148155616</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.98579435384819</v>
+        <v>27.25510838831271</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.50421825021171</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.53224127397684</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.54082866547473</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.17243092889986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.02699578213161</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51.43693987650176</v>
       </c>
     </row>
   </sheetData>
@@ -5828,25 +5828,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.74483023622204</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.09011031314319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.10602794169534</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.90812269441111</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.27768865467025</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.34555170868057</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.92842275594451</v>
+        <v>32.31741075188589</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.58864656235502</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.71965538975601</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.11093852824668</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.08478346910955</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.70094758489549</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.88578712217885</v>
       </c>
     </row>
   </sheetData>
@@ -5910,25 +5910,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.56177489862248</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.66160696172545</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.32083769531504</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.54144513833588</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.34176368703225</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.99210794097923</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.29127494456532</v>
+        <v>28.88470393685403</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.09229791760907</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.93295505200371</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.28597040286163</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.30987541429262</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.93283782860956</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.59216009987938</v>
       </c>
     </row>
   </sheetData>
@@ -5992,25 +5992,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.8992973695211</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.61357305235683</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.32570833795442</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.82099659572771</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.92386878715912</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.39317562340577</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.3289370101773</v>
+        <v>26.44927803321955</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.28275466386132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.40957647299531</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.25989439638529</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.42428259533339</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.95617761061836</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.64220924803819</v>
       </c>
     </row>
   </sheetData>
@@ -6074,25 +6074,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.2278136490438</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.45145644525217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.22980414299148</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.76864324344381</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.01481508754388</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.587712448829</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.66818467611589</v>
+        <v>32.60378338478839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.72220866794358</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.45165407421456</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.5398443751691</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.17192393421751</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.98237706894126</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.78920231492737</v>
       </c>
     </row>
   </sheetData>
@@ -6156,25 +6156,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52.2332632894895</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.02393394064085</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.13849204633384</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.73129206309773</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.76976625910891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.86645648648145</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.5645806637768</v>
+        <v>35.09443146275861</v>
+      </c>
+      <c r="C2" t="n">
+        <v>54.20683261373901</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.09899231259111</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.50256088832315</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.20869782879084</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.91058961616894</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.75400200435175</v>
       </c>
     </row>
   </sheetData>
@@ -6238,25 +6238,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.96517118697674</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.59693889816131</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.42155507700031</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.5331784318459</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.23113820464147</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.11225111713369</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.21210609686772</v>
+        <v>25.35620206548826</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.77108439765924</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.88420364481276</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.30500143745832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.02808727426475</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.62850390286314</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.5855294876724</v>
       </c>
     </row>
   </sheetData>
@@ -6320,25 +6320,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.68378171701882</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.12236623394811</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.66796182981465</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.05857155018655</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.51718066674563</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.23413839883288</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.38526819854157</v>
+        <v>22.90997036075625</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.42137636605494</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.08744044328738</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.03021097282238</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.33958019951938</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.02919781913867</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.4965608149916</v>
       </c>
     </row>
   </sheetData>
@@ -6402,25 +6402,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.79838740780244</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.80225040121301</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.28353491969218</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.43455638773888</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.94874174553047</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.55335352137845</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.53003394652885</v>
+        <v>25.80920409178784</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.07341588230322</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.19356711948434</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.06080029487914</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.01777247924024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48.19642908993134</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.93722545470631</v>
       </c>
     </row>
   </sheetData>
@@ -6484,25 +6484,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.96704073674392</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.00969452275153</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.21593434026752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.60811410683034</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.30629046670185</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.005464285304</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.34230761579653</v>
+        <v>32.82582812511928</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.29282419509533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.71851451385924</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.26611625618</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.7329621846747</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.7936642275583</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.80610090180956</v>
       </c>
     </row>
   </sheetData>
@@ -6566,25 +6566,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.13575569079753</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.61296703918386</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.45390507567112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>15.77651902530405</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.46377666152873</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.88782175845075</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.91419104120903</v>
+        <v>31.78273178384183</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.57458007782855</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.54921091112155</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.04517692435214</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.60688253012688</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.05565748635764</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.44218351299715</v>
       </c>
     </row>
   </sheetData>
@@ -6648,25 +6648,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.15539928311926</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.00162316483399</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.47631223252541</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.22984902520626</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.10303524236567</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.56184950532113</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26.0320648914578</v>
+        <v>31.43020658786489</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.49048690301972</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.24148782257612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.05856160312824</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.20621716840563</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.8161111710245</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.07185138051796</v>
       </c>
     </row>
   </sheetData>
@@ -6730,25 +6730,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.50255116465296</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.02042059902855</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.22987682398242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.82077519531452</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.42911092589032</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.93236738154493</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.10808281710679</v>
+        <v>30.96341591288718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.2536411065769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.11712106831911</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.30594583553834</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.65195041046692</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.13270105228114</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.94601346110746</v>
       </c>
     </row>
   </sheetData>
@@ -6812,25 +6812,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.85694796115768</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.14734968118692</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.86938453860996</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.03642811503314</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.35147829739639</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.35040596633639</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.34049320323427</v>
+        <v>26.83153396562141</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.91213411513265</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.62933084368676</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.80829866905662</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.22306234821554</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.44125432373357</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.99794862536547</v>
       </c>
     </row>
   </sheetData>
@@ -6894,25 +6894,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.62856083343016</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.41000783842272</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.02148200196915</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.52206276153414</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.36874913484372</v>
-      </c>
-      <c r="G2" t="n">
-        <v>57.03097013366408</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.86318275124707</v>
+        <v>38.08994616699879</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.93879119780917</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.40740408762797</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.51537407700391</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.18568349463769</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.20962693917205</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.52180287186466</v>
       </c>
     </row>
   </sheetData>
@@ -6976,25 +6976,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.64809148558184</v>
-      </c>
-      <c r="C2" t="n">
-        <v>57.6571579686204</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.2188019336679</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.17502299022347</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.69903556334544</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.25523731470314</v>
-      </c>
-      <c r="H2" t="n">
-        <v>16.60556733500423</v>
+        <v>27.1683636931932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.05777420733921</v>
+      </c>
+      <c r="D2" t="n">
+        <v>56.38298614847924</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.32242876723068</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.96529181536025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.96512600100914</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.14628545212977</v>
       </c>
     </row>
   </sheetData>
@@ -7058,25 +7058,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.78260682751998</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.67076892529251</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.23379278208647</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.92792027034975</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.04703415299072</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.04697501685621</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.13781715813526</v>
+        <v>35.29847026848025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.49622056281917</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.97112147125468</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.48487310428438</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.48396576394858</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.14296215203196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.16962230500306</v>
       </c>
     </row>
   </sheetData>
@@ -7140,25 +7140,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.00017825861349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.29817288533145</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.22961087340365</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.18963563104782</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.29683644007781</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.50298261023164</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.96783420625201</v>
+        <v>27.01776779833649</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.53185915684649</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.07579561799268</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.09192338664928</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.71866605714199</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.83087746049687</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.55475279907692</v>
       </c>
     </row>
   </sheetData>
@@ -7222,25 +7222,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.91562149618042</v>
-      </c>
-      <c r="C2" t="n">
-        <v>54.76351402580424</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.12564689380208</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.76951776321455</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.10740763829293</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.86753288786031</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.00493862793821</v>
+        <v>30.46637157799786</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.17848686411172</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.44042702729372</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.83060825045134</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.0912389452396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.27122643948627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.64732512860148</v>
       </c>
     </row>
   </sheetData>
@@ -7304,25 +7304,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.32480454897711</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.27521986870022</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.47573919288774</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.93906562973438</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.32751631309887</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.76553181783823</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.5242916143121</v>
+        <v>27.79942393601977</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.75012871686269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.46040256785311</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.10270402486899</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.08518217886023</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.47451857217915</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.42409244222367</v>
       </c>
     </row>
   </sheetData>
@@ -7386,25 +7386,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.76368666156936</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.26093348476134</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.45285142261668</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.5510170548111</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.42461902011058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.43369113159989</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.25904797512796</v>
+        <v>34.70693074602569</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.11218756109006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.70122011161992</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.82281227024409</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.25559463012186</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.66077786116958</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.02777270339224</v>
       </c>
     </row>
   </sheetData>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.17682748720354</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.17681190747557</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.88795045962169</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.45900657276604</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.26136835758379</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.55097830104975</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.11139581847064</v>
+        <v>27.33312810289837</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.43274859199261</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.67587298445197</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.37044236316586</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.99939936674521</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.18199668031156</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.71685925368132</v>
       </c>
     </row>
   </sheetData>
@@ -7550,25 +7550,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.16439128745353</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.86522158136123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.79998028185049</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.47089641790205</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.08536663493589</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.94628336319695</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.70586909552374</v>
+        <v>36.16448765600221</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.26331928367986</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.19723005812799</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.67124272344795</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.96804702425605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.15500106428239</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.69154207734426</v>
       </c>
     </row>
   </sheetData>
@@ -7632,25 +7632,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.70645771337097</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.24307630482236</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.89919646022572</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.70718193983645</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.07220874179149</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.39469653665013</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.92534324986622</v>
+        <v>27.03684154194091</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.75848640697956</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.73539028521776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.04364489762454</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.28061935037593</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.50476665271235</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.04108656085292</v>
       </c>
     </row>
   </sheetData>
@@ -7714,25 +7714,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.54447679315313</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.7687796294132</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.37166761075474</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.09056684352595</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.36442613815948</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.2622135480988</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.07798728244961</v>
+        <v>24.17117469437271</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.84260956539737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.88984086316508</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.84349439768628</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.07576157833785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.71181793748868</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.14835925866217</v>
       </c>
     </row>
   </sheetData>
@@ -7796,25 +7796,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.70669746342523</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.84415318325618</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.65203578957258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.13620503591252</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.97228699723911</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.33802913178417</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.31289788679157</v>
+        <v>18.882147084904</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.86747944697581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.41684452504072</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.83598371543466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.31796133062421</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.28103082129932</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.42476438738458</v>
       </c>
     </row>
   </sheetData>
@@ -7878,25 +7878,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.69087291160796</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.1387448700416</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.63719642529114</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.83777391794797</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.42661401289172</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.60120146296947</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.23243736681535</v>
+        <v>33.47979385783555</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.49542835224187</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.54681623992745</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.56546344623714</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.22873185602015</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.87896297365334</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.48548053608175</v>
       </c>
     </row>
   </sheetData>
@@ -7960,25 +7960,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.58473696878928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.59105242284415</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.98706367764546</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.02193056917985</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.80674224132014</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.93024479880786</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26.118863472982</v>
+        <v>30.62807072043251</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.09575838161881</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.48488812016968</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.65277915719138</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.0578385924298</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.56126556916212</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.08277353992093</v>
       </c>
     </row>
   </sheetData>
@@ -8042,25 +8042,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.37493061261838</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.73414211592547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.68196722274075</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.99934873918981</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.65384196894058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.57553848630242</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.81072127468023</v>
+        <v>38.5544463364648</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.95028263233974</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.89559792042244</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.47615943517807</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.70894731353803</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.99593425824753</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.03362359915681</v>
       </c>
     </row>
   </sheetData>
@@ -8124,25 +8124,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.39487385293767</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.14320050125001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.48760770468134</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.11402121967187</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.05646593633458</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.79565487518957</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.20103067037832</v>
+        <v>39.66747383211648</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.27985329500758</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57.90486171282058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.17707680073904</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.78217386715114</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.73180015986846</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.01880290866719</v>
       </c>
     </row>
   </sheetData>
@@ -8206,25 +8206,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.51510111551679</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.43498299583639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.3393560665977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.11605965682209</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.89252575606596</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53.27936696496035</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.32663288169496</v>
+        <v>27.11447696778353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.09993158968187</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.7943793331017</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.95801429520324</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.95998683086147</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.14663962587458</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.87040398625581</v>
       </c>
     </row>
   </sheetData>
@@ -8288,25 +8288,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.51748742252062</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.70324441534711</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.5175025765462</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.68042045356944</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.96558265431899</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.89503605765222</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.45590788249091</v>
+        <v>34.35056697908587</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.10230387908543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.37688213554623</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.81365319668732</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.40234938690517</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.06925068949683</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.57606602130382</v>
       </c>
     </row>
   </sheetData>
@@ -8370,25 +8370,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.36993310564394</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.33951560173315</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.12536059670239</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.61450618652682</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.7531658334625</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.8474475925823</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.04632890383897</v>
+        <v>42.16679915436283</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.49627865676085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.7802109103221</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.08892973304576</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.42038769208042</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.28069710428278</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.30293349275067</v>
       </c>
     </row>
   </sheetData>
@@ -8452,25 +8452,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.36700185703154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.2447315174294</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.54588888422305</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.59682098092792</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.66336378226331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.55966282545698</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.24277730396097</v>
+        <v>32.21158175845512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.25992723284946</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.2252054360026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.19896643876523</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.79777001404931</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.18835127511247</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.37096605565273</v>
       </c>
     </row>
   </sheetData>
@@ -8534,25 +8534,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.7613902809091</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.911503290423</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.04297787068311</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.76878827487639</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.79508378409913</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.35653863863966</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.97719522380162</v>
+        <v>31.06291838540982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.42058898557905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.12132469104995</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.16415190031073</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.27806936304668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.86303723966544</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.32076824215922</v>
       </c>
     </row>
   </sheetData>
@@ -8616,25 +8616,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.38433610909829</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.70651029917003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.33066618477004</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.84756743006798</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.71021014551047</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.18137239381934</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.15198520619955</v>
+        <v>24.50911259612033</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.0587963880567</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.09770764811572</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.21429979582244</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.26873783511914</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.57853993563189</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.44014821916241</v>
       </c>
     </row>
   </sheetData>
@@ -8698,25 +8698,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.28408028956034</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.18778654481044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.24961636576195</v>
-      </c>
-      <c r="E2" t="n">
-        <v>53.0391014750759</v>
-      </c>
-      <c r="F2" t="n">
-        <v>60.45769143217702</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.16604771710217</v>
-      </c>
-      <c r="H2" t="n">
-        <v>15.79661093704321</v>
+        <v>32.40829616196365</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.39196831219847</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.34335252988645</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.37451729427123</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.6716163717148</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.25998851585754</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.91933742761379</v>
       </c>
     </row>
   </sheetData>
@@ -8780,25 +8780,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.92083476440377</v>
-      </c>
-      <c r="C2" t="n">
-        <v>54.62992354900646</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.26003380064102</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.7757154816342</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.74413406527049</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.82960978326614</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.38037357688472</v>
+        <v>35.44424083432099</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.121062556965</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.15116728202504</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.39002421143099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.34058329461092</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.84958616273448</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.36354089870201</v>
       </c>
     </row>
   </sheetData>
@@ -8862,25 +8862,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.52562598373211</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.8060810763397</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.3292329777939</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.97917011731245</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.14036471980824</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.93837853819177</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.09570845764262</v>
+        <v>30.72910445210654</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.64077875939996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.13616346561736</v>
+      </c>
+      <c r="E2" t="n">
+        <v>56.7167123674022</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.04901398268412</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.85277997924449</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.2838071493293</v>
       </c>
     </row>
   </sheetData>
@@ -8944,25 +8944,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.08264633857473</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.27130182531485</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.49908513938974</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.34371866457309</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.65979407667379</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.46298748350873</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.47629621494745</v>
+        <v>34.01938221960553</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.49020038560499</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.76824805879223</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.89290550132561</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.11823731837644</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.54090718287048</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.11356186650656</v>
       </c>
     </row>
   </sheetData>
@@ -9026,25 +9026,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.47031063973393</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.75319108437112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.83539031428977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.63949421931567</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.8213489589138</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.56867995773661</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.56719290545887</v>
+        <v>27.28563343327179</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.07731184565073</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.69973940505559</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.6506464454659</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.54007460345164</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.70782435621472</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.17833422620388</v>
       </c>
     </row>
   </sheetData>
@@ -9108,25 +9108,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.14109075092584</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.99675440229083</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.83287220276019</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.68266567082296</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.55357013178799</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.78183494726325</v>
-      </c>
-      <c r="H2" t="n">
-        <v>47.90468061493402</v>
+        <v>26.10881754634214</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.60372699910034</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.29113066444147</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.98115198376488</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.32368602203682</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.22200573755739</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.45320657518431</v>
       </c>
     </row>
   </sheetData>
@@ -9190,25 +9190,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.43368906816082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.48301844243899</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.85893450907688</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.51569280991305</v>
-      </c>
-      <c r="F2" t="n">
-        <v>56.19645882974075</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.09880106279451</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.63944489663005</v>
+        <v>38.32174405342324</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.3899693857762</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.9832983240685</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.8859216399894</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.50147932668658</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.10021470314636</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.15692400186356</v>
       </c>
     </row>
   </sheetData>
@@ -9272,25 +9272,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.86080402568939</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.02981568073053</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.11371044672715</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.95667002032463</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.71683054392804</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.09907664569194</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.18776063157678</v>
+        <v>29.92122985645759</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.44353110029524</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.78665027118583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.25754804885715</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.9241969665772</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.53871877574032</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.75090836704065</v>
       </c>
     </row>
   </sheetData>
@@ -9354,25 +9354,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.68171789141488</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.87218980459702</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.59503459574076</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.56239959128379</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.79854673517358</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.01811066595645</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.17658515199836</v>
+        <v>27.15430330946671</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.25310609187425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.64300648379418</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.22901721375813</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.1445925366304</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.89036522832949</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.17673669553909</v>
       </c>
     </row>
   </sheetData>
@@ -9436,25 +9436,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.98114463834653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.16562031968006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.40897717687913</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.54673132460782</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.57808793562594</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.9325494826081</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.62135405443057</v>
+        <v>32.04935174489513</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.2764427633071</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.20771534167059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.70180055903603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.97587801636799</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.22420426356281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.7920220650235</v>
       </c>
     </row>
   </sheetData>
@@ -9518,25 +9518,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.63125845072687</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.18305970675525</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.78157599789436</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.83410486387559</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.07122029915163</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.0919017017985</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22.77740076727456</v>
+        <v>30.91707373904545</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.67213260913686</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.20184423626341</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.12617592307391</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.73781216328501</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.73910385086121</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.87925737870381</v>
       </c>
     </row>
   </sheetData>
@@ -9600,25 +9600,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.13794323402949</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.27785207487087</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.69614101007593</v>
-      </c>
-      <c r="E2" t="n">
-        <v>48.98920864398343</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.0419180410802</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.71532532006314</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.51743425746692</v>
+        <v>32.80945064212125</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.46751824682563</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.86682524139847</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.55144575009686</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.74052364788936</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.9241760007099</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.34444623264252</v>
       </c>
     </row>
   </sheetData>
@@ -9682,25 +9682,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.63974218926594</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.9107656434223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.96604674684566</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.34076105286248</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.23822448136612</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.15424698555735</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19.71429305875718</v>
+        <v>28.92954458701476</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.52861088676133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.0303094843956</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.26651069238986</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.41505461254103</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.31584635273064</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.61102177404916</v>
       </c>
     </row>
   </sheetData>
@@ -9764,25 +9764,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.43110149174716</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.22607361243877</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.85096335321079</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.26301112312092</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.60941513576329</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.79459906804852</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.2841086503583</v>
+        <v>37.08932428424695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.09710354251376</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.08278743074136</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.81244173395868</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.21056765147783</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.8033230417934</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.14950425545936</v>
       </c>
     </row>
   </sheetData>
@@ -9846,25 +9846,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.78735509146323</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.00971315196836</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.82908354070599</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.2433387275421</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.68355153552367</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.36308471387258</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.79115470126134</v>
+        <v>36.36236980561853</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.9479302591299</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.38606952955222</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.08588572411058</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.75783871880316</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23.38936916731367</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.6181913527673</v>
       </c>
     </row>
   </sheetData>
@@ -9928,25 +9928,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.35297870902252</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.14782389015967</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.05757509499443</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.93077932541654</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.81454937672601</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.0396637082567</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.92034693806643</v>
+        <v>39.56928491828958</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.1675099940103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.96172753249343</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.41112722773703</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.50035528461786</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.88599693740471</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.00817464196365</v>
       </c>
     </row>
   </sheetData>
@@ -10010,25 +10010,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.35745215858708</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.6681005834315</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.9677143540053</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.23890984335476</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.22527271196898</v>
-      </c>
-      <c r="G2" t="n">
-        <v>54.94607715503033</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.25876991956053</v>
+        <v>19.35207475855763</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.76603022520667</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.18652425536681</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.39279568692094</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.50773151067772</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.01325256832626</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.54656705939233</v>
       </c>
     </row>
   </sheetData>
@@ -10092,25 +10092,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.95234255303502</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.18034565389896</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.98083733700923</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.75504218048696</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.75923392672889</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.15578237917433</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.69374685479884</v>
+        <v>36.81854912964076</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.21458522065109</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.36398517398019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.05603211259895</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.98191453868839</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.31939170193771</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.55762554458749</v>
       </c>
     </row>
   </sheetData>
@@ -10174,25 +10174,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.06685659261675</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.8329457200345</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.09123515480479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.8504983829411</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.50250952602906</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.76237738213035</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.0104562308054</v>
+        <v>28.78510696330822</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.79726206473481</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.97548312966249</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.05227187586653</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.36661584224327</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.84380918461931</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.33743246429053</v>
       </c>
     </row>
   </sheetData>
@@ -10256,25 +10256,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.39411675877398</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.64093125627465</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.53677263227841</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.33332854732829</v>
-      </c>
-      <c r="F2" t="n">
-        <v>16.54988999039109</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48.70053666679294</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.90167737025994</v>
+        <v>33.81394890050527</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.28697584332752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.6900594851205</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.11394598130322</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.59398215401571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.85883835566001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.99457173071885</v>
       </c>
     </row>
   </sheetData>
@@ -10338,25 +10338,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.24384406416937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.92262022750382</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.16768611552828</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.85686502988726</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.73441124412422</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.74088141864841</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.8538584894502</v>
+        <v>27.70997019519567</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.83362286482199</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.83325413455652</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.66188603656448</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.35351851543867</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.90550458029887</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.92380052227414</v>
       </c>
     </row>
   </sheetData>
@@ -10420,25 +10420,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.43167444772267</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.1701941306228</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.57572161630889</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.83053519968901</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.32730313107689</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.85649398814459</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.03002207492874</v>
+        <v>31.56220995809911</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.22421457980781</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.24346197768735</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.4303562229443</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.25123897818388</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.369056848308</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.68375426031904</v>
       </c>
     </row>
   </sheetData>
@@ -10502,25 +10502,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.2181880385987</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.81480814711945</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.16887753246114</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.31410344109212</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.36290260861125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.72668150520445</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.17998940703972</v>
+        <v>41.15242412766954</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.12083315802447</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.32856666499813</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.85066426646451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.67901288587687</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.73145219596022</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.56806010932161</v>
       </c>
     </row>
   </sheetData>
@@ -10584,25 +10584,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.72584568456296</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.33746816527099</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.70546868567654</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63.94457605716145</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.09560035697374</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.85596930291531</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.26518727058294</v>
+        <v>32.90324919883142</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.69024951801317</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.68947816733865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.00175933267769</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.01797528041226</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.09417221265363</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.93950875658599</v>
       </c>
     </row>
   </sheetData>
@@ -10666,25 +10666,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.8160367508724</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.95941681456517</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.47874900518298</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.47066353353089</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.54203210225557</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.14691853018524</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.2816624621718</v>
+        <v>33.03339056161394</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.90456556711575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.60798823413135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.27383840642899</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.43801300009905</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.71174348004833</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.03486978194964</v>
       </c>
     </row>
   </sheetData>
@@ -10748,25 +10748,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.06525475496394</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.55822649620704</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.69546431654501</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.23526273688129</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.6903187827134</v>
-      </c>
-      <c r="G2" t="n">
-        <v>52.14052881161165</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.13093353217728</v>
+        <v>34.32557672426048</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.9435608690906</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57.11192350161011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.94728994559335</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.80898217654558</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.71511131549096</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.28643989129311</v>
       </c>
     </row>
   </sheetData>
@@ -10830,25 +10830,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.82989765447257</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.43654825892447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.81330237882168</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.43625506231358</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.90690778880614</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.10669012055623</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.89080807314006</v>
+        <v>35.30989984877643</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.54640879800056</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.63664191536448</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.18331718431627</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.71100154346345</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.61090843631667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.38913081438329</v>
       </c>
     </row>
   </sheetData>
@@ -10912,25 +10912,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.04541880194011</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.81817344245277</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.68138340852157</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.06398812217126</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.74939321357837</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.45066122627072</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.99881437470358</v>
+        <v>28.19198549909587</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.05711840290508</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.83794192486722</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.22143475041192</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.63197256835177</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.66055211553685</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.89683775567298</v>
       </c>
     </row>
   </sheetData>
@@ -10994,25 +10994,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.87966499584971</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.95658090041566</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.82143546549496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.98367218884275</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.17506215699296</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.89056526611605</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.97486304677442</v>
+        <v>38.27489043673231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.51835054138131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.07350239498368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.93348931067459</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.75592950911631</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.91921880321267</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.83431621701617</v>
       </c>
     </row>
   </sheetData>
@@ -11076,25 +11076,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.82968088122383</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.01336055856731</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.0671029996524</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.43446906014318</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.40009194293199</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26.12349081742915</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.63618887973863</v>
+        <v>29.37124825582753</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.36331573456318</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.94381932375573</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.50752988821939</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.15980103117277</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.80976982995681</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.69804577580226</v>
       </c>
     </row>
   </sheetData>
@@ -11158,25 +11158,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.24924326666674</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.33561474740398</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.01020660462428</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.80090680819356</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.60437976340199</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.6321976642303</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.79347041895663</v>
+        <v>38.44376643379164</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.77820987153987</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.10143104712752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.90381008355744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.4779805633915</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.18542352749048</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.0328794266504</v>
       </c>
     </row>
   </sheetData>
@@ -11240,25 +11240,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.24866376040233</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.14236686838753</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.70381727798735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.79289910301731</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.93310783953351</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.75623297651314</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.21780675807053</v>
+        <v>35.57018754357387</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.47479065455117</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.87440913303926</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.37446555937169</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.92919732663482</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.97783128594475</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.73255436961956</v>
       </c>
     </row>
   </sheetData>
@@ -11322,25 +11322,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.84470406938943</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.47300743499887</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.27810960073849</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.32444438273662</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.59800531344782</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.92185161239708</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.78433618673805</v>
+        <v>38.83814711604707</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.63082893557066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.54619730639043</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.54086143292133</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.70489212631569</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.41034159270601</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.31031011744136</v>
       </c>
     </row>
   </sheetData>
@@ -11404,25 +11404,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.09326679619474</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.87839472387981</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.93295621608845</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.40190566837363</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15.00162482334916</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.6455483540956</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20.82267505618032</v>
+        <v>21.16087227782613</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.50397215943756</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.55463818584377</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.98997883789499</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.96436535742722</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.23000367546002</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.34764251885492</v>
       </c>
     </row>
   </sheetData>
@@ -11486,25 +11486,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.53264717708997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.73945268587461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.13987268398503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.82116194065901</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.86030188060716</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.72676918290427</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.04715818733316</v>
+        <v>25.81708247700886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.79333835437694</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.33832552492316</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.15112618776251</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.94935971410889</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.48682034982807</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.74877840001955</v>
       </c>
     </row>
   </sheetData>
@@ -11568,25 +11568,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.62435169929561</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.04095865553676</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.330220843676</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.70758445978414</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.37809815743496</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.51717924838395</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.30315983439569</v>
+        <v>32.74837768095716</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.44469564398585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.49687506527338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.05764902857893</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.95916886767292</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.98979761215414</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.8129483092388</v>
       </c>
     </row>
   </sheetData>
@@ -11650,25 +11650,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.05240623549874</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.20461184343466</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.04498319815503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.27616648373627</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.89529678336409</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.93728974072054</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.3954469248666</v>
+        <v>28.07623921581498</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.89453094585387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>54.69891371568404</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.38297289969116</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.20921632098286</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.64173366874321</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.35466294241188</v>
       </c>
     </row>
   </sheetData>
@@ -11732,25 +11732,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.8978874340088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.28039712705169</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.80344096032439</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.99208051547816</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.41975362545183</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.26477889437962</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.30400423725987</v>
+        <v>30.30506197620322</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.55326995095069</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.4113790033217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.39667545888327</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.41204699236945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.54380724789848</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.01008098199279</v>
       </c>
     </row>
   </sheetData>
@@ -11814,25 +11814,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.73978694122837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.40648107034175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.92114486990388</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.25360774766948</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.95125299505585</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.65113546171928</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.24100126693202</v>
+        <v>29.63841906062704</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.042172307338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.88369020469109</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.77093822026498</v>
+      </c>
+      <c r="F2" t="n">
+        <v>53.37794700211201</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.81294189173013</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.23048359688988</v>
       </c>
     </row>
   </sheetData>
@@ -11896,25 +11896,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.28527096306671</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.02956552297037</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.97988046081138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.82895925321779</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.2605826402303</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.78483704401994</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.71350549599728</v>
+        <v>26.35055323876188</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.35415542006699</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.89859407197746</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.5592659923633</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.08963358801866</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.18141297721946</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.13330454994327</v>
       </c>
     </row>
   </sheetData>
@@ -11978,25 +11978,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.15143384924349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.0706779724296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.19464188097656</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.16470086116966</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.31770391204136</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.88114013644814</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.39534054524932</v>
+        <v>29.42443883244489</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.94566139080472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>52.07368380891268</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.82924942792531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.87096936578192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.79887163336858</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.83649093127568</v>
       </c>
     </row>
   </sheetData>
@@ -12060,25 +12060,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.42028244136687</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.5445729938088</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.24274565456136</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.51259857615037</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.25028425900919</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.31290195717426</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.58120073655144</v>
+        <v>37.83092705451833</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.55642036333573</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.31963755728034</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.53451788061989</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.98090217757456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.24864930132767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.61767315543463</v>
       </c>
     </row>
   </sheetData>
@@ -12142,25 +12142,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.6873424820762</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.21573126462884</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.74132543323065</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.25485792845198</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.6837249688273</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.24940005698625</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.39160076015164</v>
+        <v>30.25093380342184</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.10942055925563</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.68920748834985</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.18826285349283</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.37266749860087</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.04231240443887</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.63362808494212</v>
       </c>
     </row>
   </sheetData>
@@ -12224,25 +12224,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.43750302500835</v>
-      </c>
-      <c r="C2" t="n">
-        <v>60.56991840818154</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.92660834403788</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.40242802979248</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.63461337408858</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.69017370438664</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.50203231901644</v>
+        <v>28.68697260920817</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.99463490368544</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.23014426570195</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.244513698786</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.21670504328004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.66598818481459</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.08730962789748</v>
       </c>
     </row>
   </sheetData>
@@ -12306,25 +12306,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.30471685455878</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.59636300315955</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.82451540072302</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.90097082215013</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.0665873089353</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.11298563145606</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26.58669001097867</v>
+        <v>32.28489589044895</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.60822926012314</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.42230488842104</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.96093962197486</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.77091006015443</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.49621129111867</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.75276264540219</v>
       </c>
     </row>
   </sheetData>
@@ -12388,25 +12388,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.11249443719667</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.39864778877475</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.22258863498346</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.66115912222167</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.63212046564092</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.73534898236573</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21.46424391953923</v>
+        <v>29.92209693372701</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.60249098892606</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.158780461844</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.78616947927136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.32169225726255</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.62568671868764</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.68628764819455</v>
       </c>
     </row>
   </sheetData>
@@ -12470,25 +12470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.92381878203367</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.13466682660735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.46559287352783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.55969059442351</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.17998447911158</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.57351058608185</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.29905562614465</v>
+        <v>30.03707884798446</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.16350000921353</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.57546118763572</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.16539703137197</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.17568328486052</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.72912052685744</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.70290528867881</v>
       </c>
     </row>
   </sheetData>
@@ -12552,25 +12552,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.48042312392963</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.73716561073445</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.76654411504779</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.26924510048402</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.5973271164373</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48.54663453551976</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.83831811498771</v>
+        <v>22.81064774948369</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.43797120191349</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.44844681406311</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.83351097291603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.46178366314812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.17550101036222</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.12566993335904</v>
       </c>
     </row>
   </sheetData>
@@ -12634,25 +12634,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.62349435057446</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.66828318643929</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.61839935723213</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.63671637894716</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.15350972591211</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53.96886083757165</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.24885887827715</v>
+        <v>26.19040401629281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.52068639003809</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.78167718793326</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.41845840182367</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.9893629498785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.11120520721273</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.5251433277153</v>
       </c>
     </row>
   </sheetData>
@@ -12716,25 +12716,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.91459695207165</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.70956374500724</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.16004372537112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.11460932993356</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.97477707362467</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.90074136624563</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26.32350791035685</v>
+        <v>27.81628429728976</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.07527369598621</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.07354011303089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.80736986643778</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.35530526992434</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50.64817984247433</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.01894180043804</v>
       </c>
     </row>
   </sheetData>
@@ -12798,25 +12798,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.92427860096522</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.50092695043583</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.71347395792407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.8224177828176</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.43047342736863</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.90879277002989</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.0652297226825</v>
+        <v>33.62099114871528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.99626334208186</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.78295270932096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.77845618267568</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.79859896805636</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.02491773594012</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.70234337148704</v>
       </c>
     </row>
   </sheetData>
@@ -12880,25 +12880,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.46329180041193</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.14494747214991</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.22559508863296</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.77013830355094</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.3036667938284</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.85920415435948</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.49559849895927</v>
+        <v>32.75346576273002</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.33002364723306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.78927005972816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.50665733333065</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.38844644774242</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.44149293738489</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.19085803030502</v>
       </c>
     </row>
   </sheetData>
@@ -12962,25 +12962,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.46933332440919</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.33592652335147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.15053899503164</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.91169917230073</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.24874988925828</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.77417109006312</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.00560634334008</v>
+        <v>25.96101224232253</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.5993097773344</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.91773255329419</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.55266990050767</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.88371113306053</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.1873293678544</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.05088299852095</v>
       </c>
     </row>
   </sheetData>
@@ -13044,25 +13044,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.67599008219124</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.88133851778638</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.83820245124691</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.67188329443519</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.73196908681579</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22.88057027705191</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.2345107361954</v>
+        <v>34.41123424990295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.39963473518786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50.02713766711189</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.52995912635193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.93040994122262</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.94872280148655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.98292253956478</v>
       </c>
     </row>
   </sheetData>
@@ -13126,25 +13126,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.14679099326217</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.1408450657756</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.71302832718319</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.69196830998334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.16453680041445</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.93468056490168</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.2087053577071</v>
+        <v>30.95650002987696</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.39235994528737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.2205668913412</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.02092881746104</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.03319633742236</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.06903590366551</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.99678629196931</v>
       </c>
     </row>
   </sheetData>
@@ -13208,25 +13208,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.0559894396098</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.0849926743625</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.83096731830565</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.60216066112915</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.26055967154048</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.5216988905735</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.81736086417578</v>
+        <v>35.11745208459252</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.92924508548644</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.98476318463391</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.93901795133382</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.89135229918098</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.70769837530423</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.17464573207457</v>
       </c>
     </row>
   </sheetData>
@@ -13290,25 +13290,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.53147554033039</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.07420036668534</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.08722979522003</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.55313565483729</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.74221042814311</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.64021687154349</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.06609038152561</v>
+        <v>31.04382227311059</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.64280658083816</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.93091866421385</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.46982194477142</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.6876029775259</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.21265573985811</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.78945617662748</v>
       </c>
     </row>
   </sheetData>
@@ -13372,25 +13372,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.89798671862038</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.11750918701642</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.27212273839524</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.93714432790291</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.51062576990967</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.54323763454574</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.34624843258535</v>
+        <v>34.44016594872337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.92059871119511</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.21274880879912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.42641530055966</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.43881855702551</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.84648589067338</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.90418975634059</v>
       </c>
     </row>
   </sheetData>
@@ -13454,25 +13454,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.29556574803274</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.55309228144104</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.78333130110304</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.14684766693108</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.89537227012013</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.68760001856449</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.15676005816508</v>
+        <v>25.79744580140342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.18242409240691</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.98326724702459</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.45649756392968</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.48788989275697</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.73261809504231</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.2941214128592</v>
       </c>
     </row>
   </sheetData>
@@ -13536,25 +13536,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.18021772018033</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.9229061082006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.42670859103931</v>
-      </c>
-      <c r="E2" t="n">
-        <v>60.41080898289604</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.50919084494375</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.8098725761369</v>
-      </c>
-      <c r="H2" t="n">
-        <v>18.04252268108731</v>
+        <v>27.1427089961914</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.83865064288464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.38661019971286</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.15249351914038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.87946077101783</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.44318940214342</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.03551216107252</v>
       </c>
     </row>
   </sheetData>
@@ -13618,25 +13618,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.39657891200652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.9202790654101</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.89007824336895</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.56178872648416</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.82549727274086</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.81214523610209</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.32588313079251</v>
+        <v>27.80172892036908</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.79533573197529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.42274281855124</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.54858792045599</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.52483497032583</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.85134863166279</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50.49985950484569</v>
       </c>
     </row>
   </sheetData>
@@ -13700,25 +13700,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.98130381171649</v>
-      </c>
-      <c r="C2" t="n">
-        <v>57.18871546341466</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.51240603588649</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.63576755164051</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.17574361039187</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.95387689353807</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.65683915348227</v>
+        <v>42.87487052831089</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.85900753275096</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.62761363095608</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.81495508391588</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.07890571528505</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.75122127250455</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.30542581839764</v>
       </c>
     </row>
   </sheetData>
@@ -13782,25 +13782,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51.3543246736617</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.67504502369068</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.50670463751818</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.25517362712513</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.3343076596013</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.45079120705951</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20.0463752828964</v>
+        <v>33.19572647824528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.04018793768294</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.09402158945478</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.77364975476973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.50304950158287</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.75153731045811</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.45387271012078</v>
       </c>
     </row>
   </sheetData>
@@ -13864,25 +13864,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.14458579557608</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.18883360162412</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.58055058907907</v>
-      </c>
-      <c r="E2" t="n">
-        <v>58.31852214933611</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.51011776872555</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.23889347916428</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.97551437839754</v>
+        <v>26.43439230477855</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.31210993725175</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.50598603904189</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.43042999884216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.7794478949986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.7133302061925</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.22173251972784</v>
       </c>
     </row>
   </sheetData>
@@ -13946,25 +13946,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.80579052152362</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.37239918130222</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.8047793128816</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.20023016340726</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.11835949442631</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.97510646351022</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.52599703841894</v>
+        <v>43.07968323979726</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.22369057823691</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.31429117020649</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.32353267997385</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.97628301238353</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.47298667416514</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.64872441459411</v>
       </c>
     </row>
   </sheetData>
@@ -14028,25 +14028,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.36706629194597</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.46104928258336</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.04189537276459</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.92791282910621</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.02265183154993</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.01871233681584</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.06567539741341</v>
+        <v>36.53392836359448</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.34900050848071</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.76300396487293</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.88692797647055</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.5571879592547</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.77343102649002</v>
+      </c>
+      <c r="H2" t="n">
+        <v>56.82465006922435</v>
       </c>
     </row>
   </sheetData>
@@ -14110,25 +14110,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.00937713323185</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.36011430074505</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.58631954001102</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.571515997351</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.11806128719291</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.47371428183287</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.97123966386297</v>
+        <v>35.7849052030454</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.23329947267524</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.85312583419501</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.57906388299984</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.31224450911033</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.68590427494924</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.12450999850306</v>
       </c>
     </row>
   </sheetData>
@@ -14192,25 +14192,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.24483453578329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.25106194611874</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.43867257670332</v>
-      </c>
-      <c r="E2" t="n">
-        <v>48.28629026705406</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.73119015059045</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.59718875684682</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.73826723462576</v>
+        <v>35.77294177910625</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.76719633783883</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.30969497980724</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.17493323963449</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.34889147238133</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.06739306075688</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.92011987255192</v>
       </c>
     </row>
   </sheetData>
@@ -14274,25 +14274,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.82037370274516</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.15084690363996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.74252202691088</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.83325548204782</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.7757976689801</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.25781420339716</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.61097711275899</v>
+        <v>21.05196415094523</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.44645536512753</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.77274965398975</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.03865077757491</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.76158794389335</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.78250661675471</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.45486830788006</v>
       </c>
     </row>
   </sheetData>
@@ -14356,25 +14356,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.88419384293699</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.36736306347998</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.24250507072653</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.01459427297777</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.8349243172297</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.14773329373146</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.14903883018307</v>
+        <v>29.67415946366874</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.44125933487673</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.68518675345488</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.47047786149256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.58571221133254</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.24071523948774</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.22161037391645</v>
       </c>
     </row>
   </sheetData>
@@ -14438,25 +14438,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.99426783627077</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.45250941612348</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.26986364631017</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.73694865174215</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.98525046092237</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.81878463647695</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.4226099094245</v>
+        <v>30.53861507123984</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.30370296966375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.11823051730436</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.03486729659583</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.3671919207263</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.81280712269674</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.00228422789478</v>
       </c>
     </row>
   </sheetData>
@@ -14520,25 +14520,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.8709306771941</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.72540190770992</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.66421126507965</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.92374686308682</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.89926982668867</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.78260373895353</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.03790787808358</v>
+        <v>37.05315618953991</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.80220226817678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.12848223984935</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.15143484338734</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.07553976085465</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.2173020569355</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.97873161464855</v>
       </c>
     </row>
   </sheetData>
@@ -14602,25 +14602,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.50922071169477</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.79662961091526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.68115731619258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.44057186424278</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.12424360627802</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.71634753726778</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.05455981997835</v>
+        <v>34.00495031844121</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.1606041394808</v>
+      </c>
+      <c r="D2" t="n">
+        <v>55.07998405722814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.92781551020076</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.42740170796993</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.39822148002548</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.28126089695107</v>
       </c>
     </row>
   </sheetData>
@@ -14684,25 +14684,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.71621634396022</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.78971034164374</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.98462774705686</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.2336349428607</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.79652078992969</v>
-      </c>
-      <c r="G2" t="n">
-        <v>71.78831171759225</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.46361899103424</v>
+        <v>35.095597225875</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.48600438218469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.03928340931311</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.83362684797</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.3044686943999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.91167825118021</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.4067515579763</v>
       </c>
     </row>
   </sheetData>
@@ -14766,25 +14766,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.79637157080075</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.872390787789</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.83047772796078</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.22440041504456</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.60106336364741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>50.45073890756577</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.19053379996745</v>
+        <v>39.2831194733466</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.28574191705681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.39816700636902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.20250252337853</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.58665873465259</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59.69618174389834</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.23100721125547</v>
       </c>
     </row>
   </sheetData>
@@ -14848,25 +14848,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.24923563326984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.12877913161538</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.95544731129639</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.49661029354595</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.76544631215711</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.89684552458618</v>
-      </c>
-      <c r="H2" t="n">
-        <v>47.68276165365219</v>
+        <v>42.42748494235548</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.77325225903061</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.0577488748735</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.7168782365188</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.59722888963686</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.94610970952662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.08985965371116</v>
       </c>
     </row>
   </sheetData>
@@ -14930,25 +14930,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.44206054806052</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.17960243981607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.96105788402966</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.53021182540947</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.81180618622355</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.46212069718698</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.394974624674</v>
+        <v>38.95604576068946</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.7528682647032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.9847812764089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.94938077401579</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.41620596729617</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.70732171509102</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.18830371881727</v>
       </c>
     </row>
   </sheetData>
@@ -15012,25 +15012,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.64625203224853</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.10572584245496</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.48863140661224</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.49090388788134</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.66592636254882</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.88749036560857</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.81616931573863</v>
+        <v>32.18724207516637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.78231885528717</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.08212750132715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.54139579503168</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.4366905358307</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.35896549668001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.4595922604427</v>
       </c>
     </row>
   </sheetData>
@@ -15094,25 +15094,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.70139999651078</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.85799808607003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.22585434392668</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.93900767593819</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20.88228477768132</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.96106837884285</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.14957470421443</v>
+        <v>30.12682779235103</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.24436953965817</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.66677447388719</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.93323661240173</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.1852829306269</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.04846954804279</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.20235854778505</v>
       </c>
     </row>
   </sheetData>
@@ -15176,25 +15176,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.23163311222358</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.38324315221171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.73682441707204</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.0018061088126</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.75541018615261</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.17252334991543</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22.54743714955588</v>
+        <v>27.26751228380749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.07892705726201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.79036501394746</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.87483621828428</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.30543256042635</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.32676108259182</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.63406473079684</v>
       </c>
     </row>
   </sheetData>
@@ -15258,25 +15258,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.95008786170116</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.24179634594534</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.86161822977087</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.13226083637748</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.93293498912593</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.95507463063713</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.22807647056971</v>
+        <v>30.13362622428481</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.26591939760316</v>
+      </c>
+      <c r="D2" t="n">
+        <v>54.47209022251775</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.412986885641</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.22215974394456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.456430458586</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.28037713096247</v>
       </c>
     </row>
   </sheetData>
@@ -15340,25 +15340,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.51785185793755</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.78650142849493</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.67859085619497</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.66128726443416</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.59280454343892</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.75770879554254</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.57722772995919</v>
+        <v>21.63094081339234</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.88794825699798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.48045200073455</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.33451524372374</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.86879952214889</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.7363881571239</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.87639705622588</v>
       </c>
     </row>
   </sheetData>
@@ -15422,25 +15422,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.92482136664454</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.23980649235136</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.93492341227437</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.88402200170228</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.57739937778452</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.37544583686808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.07736687521881</v>
+        <v>37.60065432135416</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.32844895227803</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.608962736056</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.00191797254261</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.9859856762742</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.44580106956185</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.43132064764099</v>
       </c>
     </row>
   </sheetData>
@@ -15504,25 +15504,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01270704015921</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.84267476382885</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.80571019996496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.65852958921427</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.17887057458236</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.22860707171152</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.20205151608338</v>
+        <v>30.20990328341965</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.73797249439025</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.89527169083645</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.61898119203989</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.86264102025832</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.61056286615986</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.92727191803155</v>
       </c>
     </row>
   </sheetData>
@@ -15586,25 +15586,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.73938169801551</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.4196201009655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.41104930538507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.73506842246916</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.8149934056518</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.64893516624057</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.60261186071821</v>
+        <v>36.33234870169601</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.77083854367418</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.15144868116364</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.2078685068892</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.31228639247287</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.6249265857488</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.85012836890878</v>
       </c>
     </row>
   </sheetData>
@@ -15668,25 +15668,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.67771633433959</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.48178844189434</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.94805087458633</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.62272117131982</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.17058589024317</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.81041544996355</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.70160706678087</v>
+        <v>33.83557277732329</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.93415270624727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.59418037709703</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.25092215997618</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.28253844462377</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.52431380713625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18.74414908788368</v>
       </c>
     </row>
   </sheetData>
@@ -15750,25 +15750,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.22239358917718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.66982451608568</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.64345448733414</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.8484527294539</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.2897390433478</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.05710204457243</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.71947558073729</v>
+        <v>48.11275274179319</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.95938546875931</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.54723758374065</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.88858506301688</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.88342327722131</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.4011033531368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.17683873119291</v>
       </c>
     </row>
   </sheetData>
@@ -15832,25 +15832,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.51925168129585</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.74422895661888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.70394497378193</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.19380119677712</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.8680300050156</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.15582195315526</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.59528387531316</v>
+        <v>20.17684615094277</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.49511194901935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.19781527128799</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.18769722133295</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.16612575090025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.88206213437008</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.2292333249127</v>
       </c>
     </row>
   </sheetData>
@@ -15914,25 +15914,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.17790942921985</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.90579425532056</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.0054256127889</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.23671810355181</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.6471802916138</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.5555337665979</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.52388418532929</v>
+        <v>35.45340954211228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.14301302242716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.06963498175745</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.19613859700186</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.41041090936229</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.39084964940509</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.16583887489897</v>
       </c>
     </row>
   </sheetData>
@@ -15996,25 +15996,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.45258286274789</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.24913554211949</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.04547165837469</v>
-      </c>
-      <c r="E2" t="n">
-        <v>54.51712354924135</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.89824641435262</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.01959553337558</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.58766914931369</v>
+        <v>27.32643957835507</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.99067114585896</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.96006238521921</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.0247108721634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.15690506703057</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.0994493392265</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.74869292685461</v>
       </c>
     </row>
   </sheetData>
@@ -16078,25 +16078,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.04086189975196</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.86754918213347</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.54063456237589</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.087686412059</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.56595771472849</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.96131451462992</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.8553295227056</v>
+        <v>27.75402111948076</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.22955032811971</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.18681738942816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.22359204426575</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.23480121607326</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.26796989440653</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.96991661166302</v>
       </c>
     </row>
   </sheetData>
@@ -16160,25 +16160,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.79166448256571</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.94655764283152</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.25213112625141</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.15770065776227</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.06816040933239</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.82473185009975</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.77500809767366</v>
+        <v>33.56266314176564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.99536920072079</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.0530813273777</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.06924952032099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.21222438680704</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.10461626620892</v>
+      </c>
+      <c r="H2" t="n">
+        <v>59.02226692647773</v>
       </c>
     </row>
   </sheetData>
@@ -16242,25 +16242,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.90334946837004</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.60303170502672</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.11995948219592</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.92067121686341</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.75148587089828</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.28741561460487</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.38785639801032</v>
+        <v>27.4941570849209</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.03933377014413</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.71228791776668</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.03918739445577</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.53200369759486</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.6541302003609</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.38219985054912</v>
       </c>
     </row>
   </sheetData>
@@ -16324,25 +16324,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.99451759125772</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.80123795556722</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.60304107365292</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.99776946506473</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.35176685230553</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.61431333471439</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.42721713286518</v>
+        <v>24.37309344492941</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.70088481793467</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.93277349023965</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.41013565718853</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.46560945077986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.94165472151576</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.20759301497044</v>
       </c>
     </row>
   </sheetData>
@@ -16406,25 +16406,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.4701436631448</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.8625161527828</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.62993907498138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.15027721061157</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.87698755126912</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.40345541647864</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.66839075769003</v>
+        <v>28.27742450130976</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.65548207822533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.98975209410101</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.72229271547462</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.78145263883101</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.92710664002358</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.77794391870085</v>
       </c>
     </row>
   </sheetData>
@@ -16488,25 +16488,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.44277192435247</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.65655541384653</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.66527570207138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.62028044461503</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.00965505809362</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.45056256576354</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.75310157116665</v>
+        <v>34.82348262187254</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.62324144288556</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.33509689079947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.20363985050092</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.71155300529397</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.07463968646671</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.3165741232311</v>
       </c>
     </row>
   </sheetData>
@@ -16570,25 +16570,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.04992975594928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.45140356414387</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.9810041908489</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.06141397570583</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.05462858316993</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.06796680076224</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.2092918590951</v>
+        <v>34.1632824779271</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.14445167275306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.3712863025815</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.5652591259597</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.21261941030617</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.72412087520556</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.73676162936108</v>
       </c>
     </row>
   </sheetData>
@@ -16652,25 +16652,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.1742738398069</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.8765125672837</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.90065672075491</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.30052240070774</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.27703093104358</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.65228636743502</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.33841622860252</v>
+        <v>38.98806463571289</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.23874321800311</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.00399027245226</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.90986499203613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.66099596490213</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.43368093553651</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.22670126498016</v>
       </c>
     </row>
   </sheetData>
@@ -16734,25 +16734,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.99535952395824</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.21433268400693</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.04739156316177</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.29501035587414</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.08475209930351</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19.25843489796343</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.63846706359003</v>
+        <v>39.80411207533495</v>
+      </c>
+      <c r="C2" t="n">
+        <v>62.60539084226507</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.17556584355822</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.65821001588959</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.78533606731356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.89753506616034</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.99713743439421</v>
       </c>
     </row>
   </sheetData>
@@ -16816,25 +16816,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.57875612264408</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.71044110346372</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.81537639426701</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.71702259818344</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.68742874734356</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.62051978854077</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.00210713825156</v>
+        <v>31.38788526624242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.7505881339655</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.19897368630713</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.44156346333046</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.5757906150126</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.401277366958</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.02650472902428</v>
       </c>
     </row>
   </sheetData>
@@ -16898,25 +16898,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.28076504006192</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.22171977967569</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.97780884305288</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.31361990837492</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.56544356193891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.0439954909873</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.31795827020437</v>
+        <v>31.8914970503492</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.57800557573172</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.78097172101142</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.90867143947852</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.38083028695762</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.68732905522052</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.37324338709795</v>
       </c>
     </row>
   </sheetData>
@@ -16980,25 +16980,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.68696806915626</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.32422044875157</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.73876535077692</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.64974788982514</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.29959271832642</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.92063399241174</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23.67705235097734</v>
+        <v>33.17539329269017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.16180922713888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.42477308085368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.4925359333052</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.88323551759484</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.06957105900491</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.43352906107574</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs7_GRID13/revenue/UAVs7_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs7_GRID13/revenue/UAVs7_GRID13_Greedy.xlsx
@@ -662,25 +662,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.49316347814121</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.16955034796628</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.00324664840058</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.0441247492582</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.07489606688205</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.40833589317389</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.25368679140186</v>
+        <v>32.57418847459715</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.69834582711437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.47871720172586</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.47466601803888</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.44592652649313</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.31297013276224</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.40978185002145</v>
       </c>
     </row>
   </sheetData>
@@ -744,25 +744,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.56820737059347</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.10792165384182</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.02515140837805</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.14084825282851</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.20936858227284</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.21903444171383</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.74348546828483</v>
+        <v>48.98834531170856</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.36716311462719</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.70410829216627</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.04534593324857</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.21627849976339</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.97349901188902</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.22496576209335</v>
       </c>
     </row>
   </sheetData>
@@ -826,25 +826,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.99557704925561</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.26313587799041</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.36042600766485</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.61109375607475</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.83603679513557</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.56486894498159</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.8550035109799</v>
+        <v>28.97337328977711</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.44527762815148</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.55626764823263</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.34192793277312</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.06996091879183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.45750203344177</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.35586593201906</v>
       </c>
     </row>
   </sheetData>
@@ -908,25 +908,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.65221851107844</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.61020267496868</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.02327484005878</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.09716268026227</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.20540734089483</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.23015867634845</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.01724882192416</v>
+        <v>38.826988026081</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.30204021564505</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.13058114874354</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.16896210673666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.92594269773525</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.99489118850726</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.18741929438238</v>
       </c>
     </row>
   </sheetData>
@@ -990,25 +990,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.75797389267687</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.64922565797134</v>
-      </c>
-      <c r="D2" t="n">
-        <v>53.37426915781388</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.21400761366209</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.5840494221057</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.93869325061234</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.03279064657352</v>
+        <v>35.63601339644927</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.73876279213624</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.01236013108687</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.66214355572372</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.7360934843657</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.90198831706564</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.33408790957569</v>
       </c>
     </row>
   </sheetData>
@@ -1072,25 +1072,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.94654486530823</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.50389553505415</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.30521886361199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.44456765899604</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.34247705327588</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.76181171966364</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.30205896415264</v>
+        <v>30.82834398154104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.91323934577728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.87045494774003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.27178784547067</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.37532659010655</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.73853436258794</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.32053085735124</v>
       </c>
     </row>
   </sheetData>
@@ -1154,25 +1154,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.40154191645078</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.42350883650443</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.43397131528192</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.08083984390266</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.11879720866835</v>
-      </c>
-      <c r="G2" t="n">
-        <v>51.27352436644643</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.39303418662271</v>
+        <v>34.40960187246245</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.94168306213385</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.19713101608059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.45495417823395</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.42374310063962</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.65704769186309</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.75257743600345</v>
       </c>
     </row>
   </sheetData>
@@ -1236,25 +1236,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.28512575704318</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.44554588085013</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.70197992308049</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.53922567771456</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.25303620554306</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.64533939016857</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.75764719446076</v>
+        <v>37.62561306769732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.15763557973472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.9512657215578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.96433374961986</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.66392997736699</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.78714761114324</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.65425745742444</v>
       </c>
     </row>
   </sheetData>
@@ -1318,25 +1318,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.66502562712351</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.25406158954291</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.03023590166987</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.17848484366404</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.84133339875297</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.23229250035487</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.04019544612726</v>
+        <v>31.19064267152164</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.9805959992043</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.55548107010142</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.33162572990417</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.80198338914288</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.60366617910577</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.1619514512785</v>
       </c>
     </row>
   </sheetData>
@@ -1400,25 +1400,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.75725879759379</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.09635926157782</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.35632031381564</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.0775231683194</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.94767517624697</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.1256362384791</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.89598794305441</v>
+        <v>37.37435476916546</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50.33221040880338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.84054899609358</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.99349138896388</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.59032487023953</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.27317397142409</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.88991772109595</v>
       </c>
     </row>
   </sheetData>
@@ -1482,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.66000216663236</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.82436175908649</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50.09787100890821</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.52138436321085</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.08464849462987</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.44212054721675</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.55059753617432</v>
+        <v>20.86883305449036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.70521737750783</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.43026145534811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.60129923542983</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.09620932629661</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55.29991253117961</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.64607023072092</v>
       </c>
     </row>
   </sheetData>
@@ -1564,25 +1564,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.99488151243053</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.34143922731437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.14241445828831</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.23913300743651</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.05592779681345</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.42744255084511</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.60714208993293</v>
+        <v>36.57308442825566</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.19508172472164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.29850131048731</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.18835486459942</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.87010341876957</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.86155847890272</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.2132674029825</v>
       </c>
     </row>
   </sheetData>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.76041880280954</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.41826327184367</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.62777213117542</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.09365530760045</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.73877186089307</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.89781520933777</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.24806911328352</v>
+        <v>36.38368752762764</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.33184689777667</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.78809728431938</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.8235595032282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.09983504394259</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.65676678934209</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.58538631796559</v>
       </c>
     </row>
   </sheetData>
@@ -1728,25 +1728,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.68873912151668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.93080074632267</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.17912659533258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.31984511859839</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.87954110491869</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.68951169245769</v>
-      </c>
-      <c r="H2" t="n">
-        <v>55.23403394598958</v>
+        <v>44.53829282275098</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.71916846780134</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.20331576760235</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.04964182228318</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.38395883948671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.88129970956359</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50.65278329477351</v>
       </c>
     </row>
   </sheetData>
@@ -1810,25 +1810,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.68681324604061</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.84535132125564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.74335743221831</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.4390497192883</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.62517139184004</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.59651827243441</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.97842602129022</v>
+        <v>37.86748487180663</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.09638834671763</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.60409507489616</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.0182102279265</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.53462076735682</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.71330574262603</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.30852836727185</v>
       </c>
     </row>
   </sheetData>
@@ -1892,25 +1892,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.18280602042724</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.79910008523032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.21127630949078</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.7153429563324</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.73428320766959</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.11881541499976</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.94412919560637</v>
+        <v>34.0799406519217</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.2972097216721</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.62786304174258</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.49559957244247</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.78552824240232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.94321870543617</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.19710781248394</v>
       </c>
     </row>
   </sheetData>
@@ -1974,25 +1974,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.61142828083305</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.69335833467314</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.27382129260261</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.92869692254151</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.78005036482149</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.55462409147765</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.28143685068244</v>
+        <v>39.09378982827774</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.78811371249905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.62004742974481</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.2969870756451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.51951454232105</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.44477071180473</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.23576935235773</v>
       </c>
     </row>
   </sheetData>
@@ -2056,25 +2056,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.99047642642999</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.7881374120086</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.69940783739025</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.45864908255719</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.63821227520688</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.76891347194458</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.44334979580223</v>
+        <v>40.45346611205203</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.79894250623146</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.01222252224592</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.67732164404755</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.6092297760727</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.41198574159227</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.98162910299066</v>
       </c>
     </row>
   </sheetData>
@@ -2138,25 +2138,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.8087152586062</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.1145396638004</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.72694712426041</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.06032273339167</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.14127795088856</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.52805418314847</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.43852161436975</v>
+        <v>35.19966077560331</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.31631283620492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.8020440991758</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.95428749920978</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.35279868034102</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.15007562975781</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.98651290791989</v>
       </c>
     </row>
   </sheetData>
@@ -2220,25 +2220,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.44701762445519</v>
-      </c>
-      <c r="C2" t="n">
-        <v>59.13367754859861</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.60987122367932</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.57807115085908</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.80542911159171</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.33846407713966</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.00841783203556</v>
+        <v>35.77111257594198</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.24399506562833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.12597279644655</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.28880243545607</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.92522485033788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.04313077853786</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.35983707779766</v>
       </c>
     </row>
   </sheetData>
@@ -2302,25 +2302,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.84320438579207</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.91346543984289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.11943650665672</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.68371143694154</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.99659713062576</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.83764545059708</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50.58381301128932</v>
+        <v>49.2465944297054</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.26573212510993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.67197562332144</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.83638711607801</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.36893024750778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.53775821299508</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.85694996687852</v>
       </c>
     </row>
   </sheetData>
@@ -2384,25 +2384,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.57377544327483</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.78557947567612</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.70344175865215</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.4195101435789</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.180241829317</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.53204272657621</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.19522803973321</v>
+        <v>40.06659840046512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.92449909993811</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.31708712388189</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.08093243882115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.23908190787875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.85249242298316</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.10996025808756</v>
       </c>
     </row>
   </sheetData>
@@ -2466,25 +2466,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.56036746762787</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.21217528619853</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.03905718322945</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.57025410970996</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.11506381611894</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.6337882149272</v>
-      </c>
-      <c r="H2" t="n">
-        <v>54.15935637108271</v>
+        <v>36.21718541113026</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.96539850164582</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.08932858432217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.62249999735511</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.83061756408717</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.39042717087584</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.49879487353822</v>
       </c>
     </row>
   </sheetData>
@@ -2548,25 +2548,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.88018831287886</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.92615359828353</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.50384606041656</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.33160805731794</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.92594042285835</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.97247982646076</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.77203882577895</v>
+        <v>42.42473117645731</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.56743041854383</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.70212251312485</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.38607494537273</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.18652765467149</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54.80109579136512</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.94670237108186</v>
       </c>
     </row>
   </sheetData>
@@ -2630,25 +2630,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.94519703122737</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.36181801235553</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.27302454303494</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.88901383788298</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.32576215297041</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.35511222270566</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.80028096141713</v>
+        <v>43.35286457812197</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.7838418611928</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.03135950317805</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.08956038648145</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.75011169893485</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.73364867613689</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.59089183588629</v>
       </c>
     </row>
   </sheetData>
@@ -2712,25 +2712,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.42676443936986</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.08003389099738</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.43252670259811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.77205603841758</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.57953280067174</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.10602511242742</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.21137123575414</v>
+        <v>33.89173470989738</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.90318898537143</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.74920042421088</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.04644622893965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.45520544026377</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.26388101187879</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.56170576060332</v>
       </c>
     </row>
   </sheetData>
@@ -2794,25 +2794,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.44550058681877</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.73724469901772</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.60177243406261</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.23093662515199</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.57172378393574</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.73903574153434</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.78749842788159</v>
+        <v>28.94128064919409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48.12566581467927</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.26945626039242</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.00676185102322</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.9363226696444</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.08027124895883</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.07776328596309</v>
       </c>
     </row>
   </sheetData>
@@ -2876,25 +2876,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.34848832243589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.35392377530188</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.4553651995087</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.68558653283705</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.7118088480637</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.32573956555103</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.5136569847774</v>
+        <v>28.41518379497563</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.36499178669115</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.32751206051994</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.4249623060922</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.96590900606206</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.98662646293332</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.82546112588191</v>
       </c>
     </row>
   </sheetData>
@@ -2958,25 +2958,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.46418881861136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.9618106986708</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.94307313255707</v>
-      </c>
-      <c r="E2" t="n">
-        <v>55.74689497950804</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.23827972468774</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.86481932224477</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.91048611871987</v>
+        <v>47.97764989844418</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.51272304060321</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.53636502837465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.46813410508014</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.4768186511308</v>
+      </c>
+      <c r="G2" t="n">
+        <v>57.42934178219059</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.53799287737507</v>
       </c>
     </row>
   </sheetData>
@@ -3040,25 +3040,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.44736248460281</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.91243554573059</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.75852108874931</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.03887318166917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.74908047071024</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.21432594465035</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.81146696557609</v>
+        <v>27.87647618198589</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.06873207995173</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.60339432972366</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.34852451581103</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.16103642602016</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.61791456607914</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.08908165150868</v>
       </c>
     </row>
   </sheetData>
@@ -3122,25 +3122,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.71652785387895</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.66163599744782</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.15057538760021</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.09584014734255</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.11587295220671</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.3415643455934</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.67487610133212</v>
+        <v>34.98092847238203</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.31421638135249</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.63925501353845</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.24626578063464</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.34066070407106</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.5913296695264</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.79864788754664</v>
       </c>
     </row>
   </sheetData>
@@ -3204,25 +3204,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.76067390448774</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.50541275006556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.91564177728886</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.71940675109974</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.55275003688585</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.22441567057713</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.55739788444998</v>
+        <v>34.06047048064816</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.8579562973464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.58977518673809</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.16714536879778</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.67111608159235</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.44396566765989</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.61316245682209</v>
       </c>
     </row>
   </sheetData>
@@ -3286,25 +3286,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.16867194910421</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.34473355999246</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.4257768015658</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.37134928136449</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.25887130877595</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.50688682094431</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.98637344530344</v>
+        <v>36.99653414028991</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.10672796353354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.45497987608768</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.97997628418722</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.43211870577009</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.46390563039248</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.06841134491045</v>
       </c>
     </row>
   </sheetData>
@@ -3368,25 +3368,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.49191129769017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.16215672424661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.87373162139335</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.13334938682517</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.21901272021596</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.81444421182979</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.19627354968259</v>
+        <v>30.93283691468712</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.8241865588853</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.78288158424901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.41065344573888</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.10839870006777</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.01124178361644</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.30512395502056</v>
       </c>
     </row>
   </sheetData>
@@ -3450,25 +3450,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.04429449003088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.89639252062479</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.67829974020541</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.9089418017108</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.58185414574233</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.26474932836737</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.23881534424982</v>
+        <v>42.56827165522718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.67036774613258</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.50035356191554</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.22473941802961</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.21891684860934</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.87125866928668</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.41938875256707</v>
       </c>
     </row>
   </sheetData>
@@ -3532,25 +3532,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.08399621871876</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.15463446923637</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.9538490121719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.6948064031334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.12500853317962</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.22930501348031</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.12328506939843</v>
+        <v>32.63605119745817</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.02244746923468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.00479260412403</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.21346796144675</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.7047038312384</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.18876199742643</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.46102332000743</v>
       </c>
     </row>
   </sheetData>
@@ -3614,25 +3614,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.98904976924324</v>
-      </c>
-      <c r="C2" t="n">
-        <v>60.82570494383436</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.30455202974495</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.31335512244809</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.9907034914125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.9398103610289</v>
-      </c>
-      <c r="H2" t="n">
-        <v>49.61980035556478</v>
+        <v>33.42439002479773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.87784960737079</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.7064339419734</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.06325118985402</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.18628718488402</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.40043977551628</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.61148975992204</v>
       </c>
     </row>
   </sheetData>
@@ -3696,25 +3696,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.27332494054795</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.13449417775379</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.61064097551338</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.12314802099523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.53716054223912</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.48024064690669</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.57194607760158</v>
+        <v>40.4591213260217</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.35937904521993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.2599024529498</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.05325847982185</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.64444968809305</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.96574072661679</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.00549557651673</v>
       </c>
     </row>
   </sheetData>
@@ -3778,25 +3778,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.28542778794264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.32382735781999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.87498068142947</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.25275153854982</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.83969105366361</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.74987222614377</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.37175817139696</v>
+        <v>29.6288897084088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.65601764581399</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.44603694299158</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.7618927893549</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.48656800412208</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.16672972912923</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.36713921456904</v>
       </c>
     </row>
   </sheetData>
@@ -3860,25 +3860,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.11293870703903</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.4500346946718</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.85686194585143</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.72920942772467</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.10630255483353</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.42177538788305</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.00127127302809</v>
+        <v>36.75713570959659</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.136505016142</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.36286097452598</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.87876100186748</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.70021260921192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.93120076711826</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.63818873222889</v>
       </c>
     </row>
   </sheetData>
@@ -3942,25 +3942,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.83980740826963</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.66092558647139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.95950509842039</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.4907140683771</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.48699465711965</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.80959147493601</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.44602024095955</v>
+        <v>36.97816195747569</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.29586751075714</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.0297644752224</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.88474218820346</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.31019628127525</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.04635883502287</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.91622653134402</v>
       </c>
     </row>
   </sheetData>
@@ -4024,25 +4024,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.7367217357647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.74714052396618</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.36213474288613</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.10611604438598</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.95232961330869</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.24732683711839</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.76081245603521</v>
+        <v>32.12915690768234</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.3209262432437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.45199654320947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.28001031241986</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.84756235465789</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.30318252762146</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.09552959289021</v>
       </c>
     </row>
   </sheetData>
@@ -4106,25 +4106,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.75599568297746</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.37176424489282</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.8557654043752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.59036497936273</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.371443815327</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.67128913433771</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.93874212908572</v>
+        <v>35.85876154897912</v>
+      </c>
+      <c r="C2" t="n">
+        <v>54.54700269027063</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.01723277816727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.88972925129447</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.27310256949707</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.66165972089124</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.08696020147968</v>
       </c>
     </row>
   </sheetData>
@@ -4188,25 +4188,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.71274217089696</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.03993051278976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.39215865049666</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.120991668061</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.83820332417326</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.80899921680975</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.35919575997794</v>
+        <v>38.26177788035442</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.83969928131994</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.97305408160624</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.78654390418531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.97351275850205</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.20360590832355</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.88044441250663</v>
       </c>
     </row>
   </sheetData>
@@ -4270,25 +4270,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.01895894384506</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.47215629684388</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.50280164657505</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.9323706062006</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.76573947880872</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.70237893916728</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.06338327153911</v>
+        <v>31.90059645551134</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.66614325807279</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.08178313305429</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.17603787107461</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.5146295241303</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.47687292842243</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.7341809853837</v>
       </c>
     </row>
   </sheetData>
@@ -4352,25 +4352,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.72979830775966</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.19696735897437</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.13383445851248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.10544837133139</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.74798735594099</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53.41740470961474</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.78931598598503</v>
+        <v>38.37313041441659</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.98052247704354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.97480940626515</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.10021283480727</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.16122385839707</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.07782143728761</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.3712311754594</v>
       </c>
     </row>
   </sheetData>
@@ -4434,25 +4434,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.18958066071286</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.67752392435209</v>
-      </c>
-      <c r="D2" t="n">
-        <v>67.9102041468757</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.93239454297988</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.50326278935581</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.3086165042091</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45.82132633499743</v>
+        <v>33.88684598794044</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.53286504695855</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.14700349624489</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.62457462929864</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.81828277257996</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.9038768148252</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.92941854512378</v>
       </c>
     </row>
   </sheetData>
@@ -4516,25 +4516,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.66845895856049</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.42568541447017</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.97444277937374</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.79868449520448</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.74014995028577</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.54832309065181</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.90774932519867</v>
+        <v>26.82068412299924</v>
+      </c>
+      <c r="C2" t="n">
+        <v>60.41913131338544</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.58420105628037</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.53198248083088</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.52792299687162</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.34875827081473</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.26741702819416</v>
       </c>
     </row>
   </sheetData>
@@ -4598,25 +4598,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.24390110365069</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.12290476600373</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.72032494134098</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.07109800041552</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.48878717369437</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.19577291369733</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.71543710191004</v>
+        <v>33.56640960119867</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.62562366765932</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.89870844759102</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.51915106129626</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.30392851016649</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.81797386885856</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.80299957156889</v>
       </c>
     </row>
   </sheetData>
@@ -4680,25 +4680,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.98640359996705</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.04370890006045</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.72560593586359</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.66707818686154</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.16601761999623</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.95015030210817</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.01583449887566</v>
+        <v>41.85137969230862</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.59198880807611</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.45002484909102</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.64612303234997</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.52387089597324</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.63704087066655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.2335597871071</v>
       </c>
     </row>
   </sheetData>
@@ -4762,25 +4762,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.65459737404945</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.67803048959732</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.52065786905036</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.8706104815944</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.45034781158294</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.91613177166994</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.21788415174737</v>
+        <v>39.75061710602793</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.12027938825</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.20585502354693</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.28262442781548</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.75534096524769</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.49497010323026</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.70887320756687</v>
       </c>
     </row>
   </sheetData>
@@ -4844,25 +4844,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.42715143054543</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.54375008966307</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.9563479001546</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.65083351141363</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.12795829473637</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.45106595153446</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.16847607863347</v>
+        <v>39.70947923533405</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.87218715380716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.12695102382704</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.07057887874485</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.51658124209635</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.88819994891191</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.40336762899285</v>
       </c>
     </row>
   </sheetData>
@@ -4926,25 +4926,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.62575074595264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.05854893677877</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.83897618043776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.81053348329446</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.3815347467009</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.46632498505593</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.68743867310353</v>
+        <v>37.54374578821199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.82691469981719</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.14263867645787</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.81237006335861</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.99411744789351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.87810655951936</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.30121611585855</v>
       </c>
     </row>
   </sheetData>
@@ -5008,25 +5008,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.78264668713368</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.76370151542581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.53289586897127</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.77633079250038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.53204440241331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.34813742367628</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.59332475748324</v>
+        <v>30.97393929920045</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.58960809713281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.99784522308294</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.06102288935731</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.63761280140229</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.44958476647211</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.32944759081256</v>
       </c>
     </row>
   </sheetData>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.64822212772071</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.34746616591921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.32496569300484</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.98188806612709</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.83076654533674</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.73697317817258</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.35046340577334</v>
+        <v>23.67991335744768</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.45412319574449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.11361659795678</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.92219914855487</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.468258630117</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.21819451546898</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.24668066506394</v>
       </c>
     </row>
   </sheetData>
@@ -5172,25 +5172,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.1456164369385</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.6178000817217</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.87463932659583</v>
-      </c>
-      <c r="E2" t="n">
-        <v>54.04763716243029</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.59887659837519</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.09380666744162</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.3535900372711</v>
+        <v>35.56199663192135</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.52523511600828</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.96236882911508</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.55766295637758</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.72452376887193</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.81521143954066</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.8686760012174</v>
       </c>
     </row>
   </sheetData>
@@ -5254,25 +5254,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.90053204824778</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.24147509551833</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.46086114181126</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.89034493255706</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.90495601341645</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.06070673874726</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.61695075561205</v>
+        <v>37.85727356177516</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.12127710772475</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.78839219545617</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.82538211617651</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.48076622103033</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.95258520493845</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.2713764759168</v>
       </c>
     </row>
   </sheetData>
@@ -5336,25 +5336,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.85458104287871</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.09796428436132</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.3286813012528</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.25329680231191</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.58955709396824</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.73568809377061</v>
-      </c>
-      <c r="H2" t="n">
-        <v>47.92760279870074</v>
+        <v>31.90847486194228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.89877624579972</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.52081491020048</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.71768135890829</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.38959629029695</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.38093055835436</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.78742819632583</v>
       </c>
     </row>
   </sheetData>
@@ -5418,25 +5418,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.11096945145049</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.14104996533543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.09672952094744</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.83624841352363</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.04363530383862</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.72536596330685</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.44190310424868</v>
+        <v>31.5910756435611</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.04736062814417</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.18307204630616</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.707184716726</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.68743143088275</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.26155662876553</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.95762685226273</v>
       </c>
     </row>
   </sheetData>
@@ -5500,25 +5500,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.09563768296477</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.60108180124919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.31025793000998</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.90247921428565</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.99853681175965</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.81102850126589</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.28480642203485</v>
+        <v>34.81762806592426</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.56646809490596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.10826873618378</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.0547155878964</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.39252930444041</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.77122746353175</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.14536711503953</v>
       </c>
     </row>
   </sheetData>
@@ -5582,25 +5582,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.21182214208956</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.1233390801701</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.39757140520855</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.56459013675608</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.55408998894706</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.51192442586067</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.8046236837953</v>
+        <v>30.94657004086949</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.32289991088918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.40941256469915</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.61190860295663</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.42826588414495</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.74932503875566</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.73680114963312</v>
       </c>
     </row>
   </sheetData>
@@ -5664,25 +5664,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.02425605149507</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.58175086729833</v>
-      </c>
-      <c r="D2" t="n">
-        <v>57.91556407368697</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.3070049292194</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.24286249259266</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.67667674553378</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.26827994294196</v>
+        <v>45.39794055812439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.81813438932181</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.21362150820335</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.12438919622215</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.98336641585126</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.96193559527318</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.59251954388275</v>
       </c>
     </row>
   </sheetData>
@@ -5746,25 +5746,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.25510838831271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.50421825021171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.53224127397684</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.54082866547473</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.17243092889986</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.02699578213161</v>
-      </c>
-      <c r="H2" t="n">
-        <v>51.43693987650176</v>
+        <v>36.80638337174179</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.63291596960774</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.65975250818543</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.16103007406102</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.38684330098986</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.07570387575736</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.28034543153163</v>
       </c>
     </row>
   </sheetData>
@@ -5828,25 +5828,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.31741075188589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.58864656235502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.71965538975601</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.11093852824668</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.08478346910955</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.70094758489549</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.88578712217885</v>
+        <v>33.35250940488877</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.1712729555205</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.97575381465953</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.51464472082239</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.45602407604292</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.4653717619178</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.06438604000038</v>
       </c>
     </row>
   </sheetData>
@@ -5910,25 +5910,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.88470393685403</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.09229791760907</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.93295505200371</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.28597040286163</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.30987541429262</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.93283782860956</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.59216009987938</v>
+        <v>39.1329712347218</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.85788847284476</v>
+      </c>
+      <c r="D2" t="n">
+        <v>52.29632313035988</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.05190664608914</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.15212833109712</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.94118452329447</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.1204471381978</v>
       </c>
     </row>
   </sheetData>
@@ -5992,25 +5992,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.44927803321955</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.28275466386132</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.40957647299531</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.25989439638529</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.42428259533339</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.95617761061836</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.64220924803819</v>
+        <v>32.25544249653572</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.66107579463819</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.84887062913448</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.72791367203376</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.94483513814379</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.33750125522122</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.13117502243332</v>
       </c>
     </row>
   </sheetData>
@@ -6074,25 +6074,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.60378338478839</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.72220866794358</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.45165407421456</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.5398443751691</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.17192393421751</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.98237706894126</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.78920231492737</v>
+        <v>37.46327011255493</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.67600600134507</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.1270391744671</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.89986614450334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.53344221269763</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.31280556809281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.28380049692673</v>
       </c>
     </row>
   </sheetData>
@@ -6156,25 +6156,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.09443146275861</v>
-      </c>
-      <c r="C2" t="n">
-        <v>54.20683261373901</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.09899231259111</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.50256088832315</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.20869782879084</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.91058961616894</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.75400200435175</v>
+        <v>41.03825732070285</v>
+      </c>
+      <c r="C2" t="n">
+        <v>54.66749035236311</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.32752575530583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.25650497153343</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.31546643325827</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.35194868619627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.99275659351477</v>
       </c>
     </row>
   </sheetData>
@@ -6238,25 +6238,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.35620206548826</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.77108439765924</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.88420364481276</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.30500143745832</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.02808727426475</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.62850390286314</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.5855294876724</v>
+        <v>31.47559272410561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.93106504008954</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.00243099739146</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.91264543298892</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.53005982964648</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.47642218988374</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22.68045546723267</v>
       </c>
     </row>
   </sheetData>
@@ -6320,25 +6320,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.90997036075625</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.42137636605494</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.08744044328738</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.03021097282238</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.33958019951938</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.02919781913867</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.4965608149916</v>
+        <v>36.33173643809981</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.81391290082097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.87508190172126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.31079278694057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.3681682718858</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.22838930405649</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.64417313967694</v>
       </c>
     </row>
   </sheetData>
@@ -6402,25 +6402,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.80920409178784</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.07341588230322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.19356711948434</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.06080029487914</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.01777247924024</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48.19642908993134</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.93722545470631</v>
+        <v>31.77759060503627</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.8253791088497</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.83328461789247</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.76609654438816</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.36171621608987</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.38943114385624</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.67890143235147</v>
       </c>
     </row>
   </sheetData>
@@ -6484,25 +6484,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.82582812511928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.29282419509533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.71851451385924</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.26611625618</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.7329621846747</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.7936642275583</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.80610090180956</v>
+        <v>34.37409810379641</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.01296642978149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.41864401386915</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.84010316740704</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.30521706807913</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.15214272927962</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.66111145629038</v>
       </c>
     </row>
   </sheetData>
@@ -6566,25 +6566,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.78273178384183</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.57458007782855</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.54921091112155</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.04517692435214</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.60688253012688</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.05565748635764</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.44218351299715</v>
+        <v>50.20318022871549</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.7612230986653</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.92999211726368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.45780351402855</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.32494228552208</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.04682281790143</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.30993458525123</v>
       </c>
     </row>
   </sheetData>
@@ -6648,25 +6648,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.43020658786489</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.49048690301972</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.24148782257612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.05856160312824</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.20621716840563</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.8161111710245</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.07185138051796</v>
+        <v>34.19737293862203</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.34219947451701</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.31935150325751</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.40953858865272</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.33640734391397</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.00327430670572</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.67625604785269</v>
       </c>
     </row>
   </sheetData>
@@ -6730,25 +6730,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.96341591288718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.2536411065769</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.11712106831911</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.30594583553834</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.65195041046692</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.13270105228114</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.94601346110746</v>
+        <v>26.4945832525084</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.69318957769201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.89009876336906</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.84615565881541</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.1652827727846</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.14833561022446</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.6171631240453</v>
       </c>
     </row>
   </sheetData>
@@ -6812,25 +6812,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.83153396562141</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.91213411513265</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.62933084368676</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.80829866905662</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.22306234821554</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.44125432373357</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.99794862536547</v>
+        <v>30.2451708924923</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.16567866996242</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.88359033845216</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.80618301656944</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.19254820060539</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.07069815763399</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.88606291106878</v>
       </c>
     </row>
   </sheetData>
@@ -6894,25 +6894,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.08994616699879</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.93879119780917</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.40740408762797</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.51537407700391</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.18568349463769</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.20962693917205</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.52180287186466</v>
+        <v>37.14800854986855</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.76011260761283</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.30465922116547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.15554161020582</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.90406970095465</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.02327978205633</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.38748406892832</v>
       </c>
     </row>
   </sheetData>
@@ -6976,25 +6976,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.1683636931932</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.05777420733921</v>
-      </c>
-      <c r="D2" t="n">
-        <v>56.38298614847924</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.32242876723068</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.96529181536025</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.96512600100914</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.14628545212977</v>
+        <v>32.9908616116279</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.22242012025762</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.59776066718516</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.66708096872355</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.44681307365682</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.15247481090746</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.44971113559021</v>
       </c>
     </row>
   </sheetData>
@@ -7058,25 +7058,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.29847026848025</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.49622056281917</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.97112147125468</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.48487310428438</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.48396576394858</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.14296215203196</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.16962230500306</v>
+        <v>37.20783543684757</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.95315706435294</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.50285531128949</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.62180367051886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.76252279058621</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.94936050749174</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.05251008944857</v>
       </c>
     </row>
   </sheetData>
@@ -7140,25 +7140,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.01776779833649</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.53185915684649</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.07579561799268</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.09192338664928</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.71866605714199</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.83087746049687</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.55475279907692</v>
+        <v>41.77902639790259</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.24919151134782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.09600280130367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.52496691311632</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.60560652862661</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.66323482723968</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.92409743546673</v>
       </c>
     </row>
   </sheetData>
@@ -7222,25 +7222,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.46637157799786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.17848686411172</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.44042702729372</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.83060825045134</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48.0912389452396</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.27122643948627</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.64732512860148</v>
+        <v>33.05881550933705</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.69806337488889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.8040913792103</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.86491197835446</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.4274555041243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.54585515315699</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.95243901786049</v>
       </c>
     </row>
   </sheetData>
@@ -7304,25 +7304,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.79942393601977</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.75012871686269</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.46040256785311</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.10270402486899</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.08518217886023</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.47451857217915</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.42409244222367</v>
+        <v>37.7622486316148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.40975435843442</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.02986982999141</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.69330883877263</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.36917497891839</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.86362145800424</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.72788797075967</v>
       </c>
     </row>
   </sheetData>
@@ -7386,25 +7386,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.70693074602569</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.11218756109006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.70122011161992</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.82281227024409</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.25559463012186</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.66077786116958</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.02777270339224</v>
+        <v>34.73662481152406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.82618543658962</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.41667269841182</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.56125105402167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.11800044509779</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.79214791054734</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.92188181489185</v>
       </c>
     </row>
   </sheetData>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.33312810289837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.43274859199261</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.67587298445197</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.37044236316586</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.99939936674521</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.18199668031156</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.71685925368132</v>
+        <v>36.42885205311963</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.70442291141817</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.46757073778997</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.16382453667216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.54207569753601</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.34384646882674</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.5496538066015</v>
       </c>
     </row>
   </sheetData>
@@ -7550,25 +7550,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.16448765600221</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.26331928367986</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.19723005812799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>49.67124272344795</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.96804702425605</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.15500106428239</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.69154207734426</v>
+        <v>37.0987606436098</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.23463291938713</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.51305084939913</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.15916895456765</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.44663700426282</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.27131566039494</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.89149460246466</v>
       </c>
     </row>
   </sheetData>
@@ -7632,25 +7632,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.03684154194091</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.75848640697956</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.73539028521776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.04364489762454</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.28061935037593</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.50476665271235</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.04108656085292</v>
+        <v>36.3746660569843</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.3075443125594</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.4487955686114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.89827047269403</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.50937211231716</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.71981908000128</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.6996929883488</v>
       </c>
     </row>
   </sheetData>
@@ -7714,25 +7714,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.17117469437271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.84260956539737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.88984086316508</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.84349439768628</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.07576157833785</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.71181793748868</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.14835925866217</v>
+        <v>32.79657799585929</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.7232377463935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51.25508855516492</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.47380177681631</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.32887415280587</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.81097338540305</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.88827588500425</v>
       </c>
     </row>
   </sheetData>
@@ -7796,25 +7796,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.882147084904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.86747944697581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.41684452504072</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.83598371543466</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.31796133062421</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.28103082129932</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.42476438738458</v>
+        <v>43.57545961889703</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.98009539943131</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.57254354069579</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.38953813732896</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.68960930770869</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.28970463623333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.54808866855882</v>
       </c>
     </row>
   </sheetData>
@@ -7878,25 +7878,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.47979385783555</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.49542835224187</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.54681623992745</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.56546344623714</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.22873185602015</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.87896297365334</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29.48548053608175</v>
+        <v>35.17534445059446</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50.60817894356361</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.26843695967768</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.46174942258166</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.79482847500352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.77278342743448</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.51332894014137</v>
       </c>
     </row>
   </sheetData>
@@ -7960,25 +7960,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.62807072043251</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.09575838161881</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.48488812016968</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.65277915719138</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.0578385924298</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.56126556916212</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.08277353992093</v>
+        <v>28.03541950878214</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.90549651862935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.49526114889942</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.51226323613397</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.93056318753329</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.87883744348222</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.68312420692344</v>
       </c>
     </row>
   </sheetData>
@@ -8042,25 +8042,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.5544463364648</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.95028263233974</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.89559792042244</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.47615943517807</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.70894731353803</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.99593425824753</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.03362359915681</v>
+        <v>37.32329282713484</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.22290955563879</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.22097360554916</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.69875213610923</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.6802069134326</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54.68817123039583</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.16776249720861</v>
       </c>
     </row>
   </sheetData>
@@ -8124,25 +8124,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.66747383211648</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.27985329500758</v>
-      </c>
-      <c r="D2" t="n">
-        <v>57.90486171282058</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.17707680073904</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.78217386715114</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.73180015986846</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21.01880290866719</v>
+        <v>36.38822594936358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.75855610973221</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.16757238766807</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.69618437525375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.30960469700696</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.29859102623013</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.30736791488414</v>
       </c>
     </row>
   </sheetData>
@@ -8206,25 +8206,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.11447696778353</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.09993158968187</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.7943793331017</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.95801429520324</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.95998683086147</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.14663962587458</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.87040398625581</v>
+        <v>39.70649832058465</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.84580568073664</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.1274476162754</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.61807035166586</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.49754481381964</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.61030284721483</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.78995694221442</v>
       </c>
     </row>
   </sheetData>
@@ -8288,25 +8288,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.35056697908587</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.10230387908543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.37688213554623</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.81365319668732</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.40234938690517</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.06925068949683</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.57606602130382</v>
+        <v>31.03158888984316</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.83503909492356</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.38718177411617</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.69233000167466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.97743495483591</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.39106269960889</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.35143736142069</v>
       </c>
     </row>
   </sheetData>
@@ -8370,25 +8370,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.16679915436283</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.49627865676085</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.7802109103221</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.08892973304576</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.42038769208042</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.28069710428278</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.30293349275067</v>
+        <v>40.17316089899616</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.01531898481992</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.12501835627059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.87558407888018</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.87275880988958</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.24575433942586</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.60839859027419</v>
       </c>
     </row>
   </sheetData>
@@ -8452,25 +8452,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.21158175845512</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.25992723284946</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.2252054360026</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.19896643876523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.79777001404931</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.18835127511247</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.37096605565273</v>
+        <v>39.66830797898028</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.96186803694881</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.75358820676293</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.73823423980775</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.20153106188694</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.91769726784116</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.08260718693774</v>
       </c>
     </row>
   </sheetData>
@@ -8534,25 +8534,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.06291838540982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.42058898557905</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.12132469104995</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.16415190031073</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.27806936304668</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.86303723966544</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.32076824215922</v>
+        <v>40.82230543086372</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.99548772653708</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.85949206856732</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.27890809512903</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.4443160700937</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.82248812670272</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.21879223032126</v>
       </c>
     </row>
   </sheetData>
@@ -8616,25 +8616,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.50911259612033</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.0587963880567</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.09770764811572</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.21429979582244</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.26873783511914</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.57853993563189</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.44014821916241</v>
+        <v>36.03811836932839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.05892131390677</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.54058378827334</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.43498292521799</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.29605449940816</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.60356319117813</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.73507487965614</v>
       </c>
     </row>
   </sheetData>
@@ -8698,25 +8698,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.40829616196365</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.39196831219847</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.34335252988645</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.37451729427123</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.6716163717148</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.25998851585754</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.91933742761379</v>
+        <v>38.8544029134223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.96204144914127</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.62675216945587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.03846004630277</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.95795529671293</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.12954637668077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.59328104706717</v>
       </c>
     </row>
   </sheetData>
@@ -8780,25 +8780,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.44424083432099</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.121062556965</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.15116728202504</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.39002421143099</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.34058329461092</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.84958616273448</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.36354089870201</v>
+        <v>36.36414647191452</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.95660021330219</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.04957679281328</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.01022527363753</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.97836508157321</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.70426091120663</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.6397091527831</v>
       </c>
     </row>
   </sheetData>
@@ -8862,25 +8862,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.72910445210654</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.64077875939996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.13616346561736</v>
-      </c>
-      <c r="E2" t="n">
-        <v>56.7167123674022</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.04901398268412</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.85277997924449</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.2838071493293</v>
+        <v>30.16666819344195</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.00327685634199</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.90203536016916</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.423064484574</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.28674330324198</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.56385201651466</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.51630721307331</v>
       </c>
     </row>
   </sheetData>
@@ -8944,25 +8944,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.01938221960553</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.49020038560499</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.76824805879223</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.89290550132561</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.11823731837644</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.54090718287048</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.11356186650656</v>
+        <v>29.72171458659521</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.39159241758558</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.90688790067825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.80599320560258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.08448691785077</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.90577650137973</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.13388062200178</v>
       </c>
     </row>
   </sheetData>
@@ -9026,25 +9026,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28563343327179</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.07731184565073</v>
-      </c>
-      <c r="D2" t="n">
-        <v>53.69973940505559</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.6506464454659</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.54007460345164</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.70782435621472</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.17833422620388</v>
+        <v>35.14635442892985</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.54121204197054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.26250386404747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.74034063699272</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.7349076274413</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.63421405868245</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.12906052138072</v>
       </c>
     </row>
   </sheetData>
@@ -9108,25 +9108,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.10881754634214</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.60372699910034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.29113066444147</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.98115198376488</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.32368602203682</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.22200573755739</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.45320657518431</v>
+        <v>31.87667288569058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.51969237365664</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.73476931281666</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.72410596683361</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.98138709421756</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.42366386900444</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.24694529400752</v>
       </c>
     </row>
   </sheetData>
@@ -9190,25 +9190,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.32174405342324</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.3899693857762</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.9832983240685</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.8859216399894</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.50147932668658</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.10021470314636</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.15692400186356</v>
+        <v>29.84884558276162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.62958237253827</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.29329140719148</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.72090327932875</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.74551753284364</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.09492051831668</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.32010331737045</v>
       </c>
     </row>
   </sheetData>
@@ -9272,25 +9272,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.92122985645759</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.44353110029524</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.78665027118583</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.25754804885715</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48.9241969665772</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.53871877574032</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.75090836704065</v>
+        <v>36.18772695295763</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.59667205497255</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.76509175118951</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55.74930890060621</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.85241807215434</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.90467888620638</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.37977826699912</v>
       </c>
     </row>
   </sheetData>
@@ -9354,25 +9354,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.15430330946671</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.25310609187425</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.64300648379418</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.22901721375813</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.1445925366304</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.89036522832949</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.17673669553909</v>
+        <v>33.01094442713686</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.95392145595425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.29780950326324</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.58440734584411</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.86071941621381</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.0666591267378</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.11623161398749</v>
       </c>
     </row>
   </sheetData>
@@ -9436,25 +9436,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.04935174489513</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.2764427633071</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.20771534167059</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.70180055903603</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.97587801636799</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.22420426356281</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.7920220650235</v>
+        <v>36.78549597785009</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.66079466714017</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.10077401239594</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.09817433042209</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.49820628560639</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.57427641186823</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.0177714533046</v>
       </c>
     </row>
   </sheetData>
@@ -9518,25 +9518,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.91707373904545</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.67213260913686</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.20184423626341</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.12617592307391</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.73781216328501</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.73910385086121</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.87925737870381</v>
+        <v>37.48035792263176</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.22328137405371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.39440593534686</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.53193268043978</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.08538225826937</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.21103711534163</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.1766107295169</v>
       </c>
     </row>
   </sheetData>
@@ -9600,25 +9600,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.80945064212125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.46751824682563</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.86682524139847</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.55144575009686</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.74052364788936</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.9241760007099</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.34444623264252</v>
+        <v>42.00091993293369</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.66693908795093</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.87463712671098</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.08177576187965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.69121425228293</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.8851511918126</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.07465094124691</v>
       </c>
     </row>
   </sheetData>
@@ -9682,25 +9682,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.92954458701476</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.52861088676133</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.0303094843956</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.26651069238986</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.41505461254103</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.31584635273064</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.61102177404916</v>
+        <v>40.9321527867829</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.38291151500304</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.37590176230535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.18657314203342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.79072983301477</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.51058275972599</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.17725600170208</v>
       </c>
     </row>
   </sheetData>
@@ -9764,25 +9764,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.08932428424695</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.09710354251376</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.08278743074136</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.81244173395868</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.21056765147783</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.8033230417934</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.14950425545936</v>
+        <v>50.05616074596682</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.19507349018144</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.03292313766169</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.17261645267218</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.52736818646233</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.4173678293232</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.58458990442432</v>
       </c>
     </row>
   </sheetData>
@@ -9846,25 +9846,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.36236980561853</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.9479302591299</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.38606952955222</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.08588572411058</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.75783871880316</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.38936916731367</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.6181913527673</v>
+        <v>30.10747664086116</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.90315890244021</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.32375881746494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.84186303778258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.81922768554571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.03103170207698</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.06285868978983</v>
       </c>
     </row>
   </sheetData>
@@ -9928,25 +9928,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.56928491828958</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.1675099940103</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.96172753249343</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.41112722773703</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.50035528461786</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.88599693740471</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.00817464196365</v>
+        <v>32.3748075972528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.50059460729639</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.65723878111672</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.64623991666583</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.15543571467695</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54.60276922634278</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.02147167176609</v>
       </c>
     </row>
   </sheetData>
@@ -10010,25 +10010,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.35207475855763</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.76603022520667</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.18652425536681</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.39279568692094</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.50773151067772</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.01325256832626</v>
-      </c>
-      <c r="H2" t="n">
-        <v>49.54656705939233</v>
+        <v>41.18101621045727</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.78490965637963</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.73282754568752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.39445073967634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.94079624316294</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.83883441618863</v>
+      </c>
+      <c r="H2" t="n">
+        <v>47.5000441767271</v>
       </c>
     </row>
   </sheetData>
@@ -10092,25 +10092,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.81854912964076</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.21458522065109</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.36398517398019</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.05603211259895</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.98191453868839</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.31939170193771</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.55762554458749</v>
+        <v>36.22855860912104</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.1729547648516</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.17778520536929</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.22776665609081</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.82220034940051</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.49954474014022</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.0622254006969</v>
       </c>
     </row>
   </sheetData>
@@ -10174,25 +10174,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.78510696330822</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.79726206473481</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.97548312966249</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.05227187586653</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.36661584224327</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.84380918461931</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.33743246429053</v>
+        <v>36.06463398343046</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.33308191679766</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.10073079260078</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.51141139668256</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.41423475551336</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.91667191576237</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.09326889107961</v>
       </c>
     </row>
   </sheetData>
@@ -10256,25 +10256,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.81394890050527</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.28697584332752</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.6900594851205</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.11394598130322</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.59398215401571</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.85883835566001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.99457173071885</v>
+        <v>38.81968488567487</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.69319734140178</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.97325061888289</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.98198853823506</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.74860930193523</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.43588603966458</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28.1042951578008</v>
       </c>
     </row>
   </sheetData>
@@ -10338,25 +10338,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.70997019519567</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.83362286482199</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.83325413455652</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.66188603656448</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.35351851543867</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.90550458029887</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.92380052227414</v>
+        <v>35.87898325442036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.9621118186089</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.16600698481179</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.11530184141025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.6238594023983</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.22620137952013</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.048501198659</v>
       </c>
     </row>
   </sheetData>
@@ -10420,25 +10420,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.56220995809911</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.22421457980781</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.24346197768735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.4303562229443</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.25123897818388</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.369056848308</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.68375426031904</v>
+        <v>47.54330206261604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.68447943125015</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.00455130620556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.66156283405319</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.70665960524959</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.45711163808227</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.94278637536793</v>
       </c>
     </row>
   </sheetData>
@@ -10502,25 +10502,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.15242412766954</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.12083315802447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.32856666499813</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.85066426646451</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.67901288587687</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.73145219596022</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.56806010932161</v>
+        <v>34.13894908462538</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.10737839491919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.37740610270309</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.84376263593037</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.70728247702034</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.08165794586363</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.72345664686931</v>
       </c>
     </row>
   </sheetData>
@@ -10584,25 +10584,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.90324919883142</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.69024951801317</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.68947816733865</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.00175933267769</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.01797528041226</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.09417221265363</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.93950875658599</v>
+        <v>38.6896076002545</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.53733990317937</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.89082077953633</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.8805120457757</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.37447989684447</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.37695396492857</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.51215818290558</v>
       </c>
     </row>
   </sheetData>
@@ -10666,25 +10666,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.03339056161394</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.90456556711575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.60798823413135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.27383840642899</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.43801300009905</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.71174348004833</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.03486978194964</v>
+        <v>62.45743548056409</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.48859699697574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.59529286148565</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.87484057145883</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.45018717777597</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.64051365371138</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.65706326403167</v>
       </c>
     </row>
   </sheetData>
@@ -10748,25 +10748,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.32557672426048</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.9435608690906</v>
-      </c>
-      <c r="D2" t="n">
-        <v>57.11192350161011</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.94728994559335</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.80898217654558</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.71511131549096</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.28643989129311</v>
+        <v>47.28856580249573</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.18280503866364</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.67460905523225</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.14666792874105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.99380112697676</v>
+      </c>
+      <c r="G2" t="n">
+        <v>61.79163051770468</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.26098151164821</v>
       </c>
     </row>
   </sheetData>
@@ -10830,25 +10830,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.30989984877643</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.54640879800056</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.63664191536448</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.18331718431627</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.71100154346345</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.61090843631667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.38913081438329</v>
+        <v>29.60315349142088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.86586702896039</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.02590944415062</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.3472007616794</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.60412978264004</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.84394970081878</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.79271254834039</v>
       </c>
     </row>
   </sheetData>
@@ -10912,25 +10912,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.19198549909587</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.05711840290508</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.83794192486722</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.22143475041192</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.63197256835177</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.66055211553685</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45.89683775567298</v>
+        <v>32.27642031563015</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.72987848655909</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.7879965064437</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.00985651251178</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.13005597837108</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.41812424128611</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.72300145900537</v>
       </c>
     </row>
   </sheetData>
@@ -10994,25 +10994,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.27489043673231</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.51835054138131</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.07350239498368</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.93348931067459</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.75592950911631</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.91921880321267</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.83431621701617</v>
+        <v>38.82675434663108</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.3246763058482</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.34794255891019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.92803836154933</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.07794874052685</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.18705344691848</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.2761495444251</v>
       </c>
     </row>
   </sheetData>
@@ -11076,25 +11076,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.37124825582753</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.36331573456318</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.94381932375573</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.50752988821939</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.15980103117277</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.80976982995681</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.69804577580226</v>
+        <v>41.82408258575716</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.1125202375083</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.81448075903374</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.52485189029348</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.36155361526296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.85219450910784</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.70786846050508</v>
       </c>
     </row>
   </sheetData>
@@ -11158,25 +11158,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.44376643379164</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.77820987153987</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.10143104712752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.90381008355744</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.4779805633915</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.18542352749048</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.0328794266504</v>
+        <v>39.81142221941023</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.45559072291864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.61119325449741</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.60187235023744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.47479247624911</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50.78679302564708</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.08521987715228</v>
       </c>
     </row>
   </sheetData>
@@ -11240,25 +11240,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.57018754357387</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.47479065455117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.87440913303926</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.37446555937169</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.92919732663482</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.97783128594475</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.73255436961956</v>
+        <v>38.39445963225356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.36362229609493</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.28008872282152</v>
+      </c>
+      <c r="E2" t="n">
+        <v>68.98309012771476</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.52247105286608</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.14053478866806</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.59404430149679</v>
       </c>
     </row>
   </sheetData>
@@ -11322,25 +11322,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.83814711604707</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.63082893557066</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.54619730639043</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.54086143292133</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.70489212631569</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.41034159270601</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.31031011744136</v>
+        <v>48.33223340607586</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.56481069321935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.70043496685526</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.37049346186704</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.53917749518538</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.73146692249148</v>
+      </c>
+      <c r="H2" t="n">
+        <v>47.39945833259388</v>
       </c>
     </row>
   </sheetData>
@@ -11404,25 +11404,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.16087227782613</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.50397215943756</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.55463818584377</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.98997883789499</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.96436535742722</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.23000367546002</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.34764251885492</v>
+        <v>36.15446324877383</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.2044011627475</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.18116396165545</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.35177462192321</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.45140206759584</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23.77372620314648</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.16260010194402</v>
       </c>
     </row>
   </sheetData>
@@ -11486,25 +11486,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.81708247700886</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.79333835437694</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.33832552492316</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.15112618776251</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.94935971410889</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.48682034982807</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.74877840001955</v>
+        <v>39.71277002493729</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.26605205750149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.5026786834157</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.90493833861532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.8913540045887</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.65078414799942</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.66840285827848</v>
       </c>
     </row>
   </sheetData>
@@ -11568,25 +11568,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.74837768095716</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.44469564398585</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.49687506527338</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.05764902857893</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.95916886767292</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.98979761215414</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.8129483092388</v>
+        <v>34.28854961535555</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.54323185900988</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.51072745443455</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.12304909736549</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.72932917544886</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.34159751771823</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.78409484240349</v>
       </c>
     </row>
   </sheetData>
@@ -11650,25 +11650,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.07623921581498</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.89453094585387</v>
-      </c>
-      <c r="D2" t="n">
-        <v>54.69891371568404</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.38297289969116</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.20921632098286</v>
-      </c>
-      <c r="G2" t="n">
-        <v>47.64173366874321</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.35466294241188</v>
+        <v>36.53077386148045</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.81318837720324</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.72029182354289</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.86306516570227</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.56593583556734</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.24393328901935</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.81020361244192</v>
       </c>
     </row>
   </sheetData>
@@ -11732,25 +11732,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.30506197620322</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.55326995095069</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.4113790033217</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.39667545888327</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.41204699236945</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.54380724789848</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.01008098199279</v>
+        <v>37.47680375449563</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.14533831739585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.33047289979243</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.95799332028832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.30424962121073</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.51442501831097</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.91423805686237</v>
       </c>
     </row>
   </sheetData>
@@ -11814,25 +11814,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.63841906062704</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.042172307338</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.88369020469109</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.77093822026498</v>
-      </c>
-      <c r="F2" t="n">
-        <v>53.37794700211201</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.81294189173013</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.23048359688988</v>
+        <v>35.73613835660851</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.71335788464601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.93678399445499</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48.36158416392315</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.64379199587695</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.35336927514508</v>
+      </c>
+      <c r="H2" t="n">
+        <v>43.95029748553191</v>
       </c>
     </row>
   </sheetData>
@@ -11896,25 +11896,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.35055323876188</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.35415542006699</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.89859407197746</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.5592659923633</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.08963358801866</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.18141297721946</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.13330454994327</v>
+        <v>31.53733725184401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.51870028379133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.97454477851841</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.51202012883265</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.15861805019382</v>
+      </c>
+      <c r="G2" t="n">
+        <v>52.0234183229022</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.93918038795992</v>
       </c>
     </row>
   </sheetData>
@@ -11978,25 +11978,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.42443883244489</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.94566139080472</v>
-      </c>
-      <c r="D2" t="n">
-        <v>52.07368380891268</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.82924942792531</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.87096936578192</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.79887163336858</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.83649093127568</v>
+        <v>38.28782172725287</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.18668024575236</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.23511530686874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.81601269097206</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.57741113936927</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.35174734398806</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.52257643411976</v>
       </c>
     </row>
   </sheetData>
@@ -12060,25 +12060,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.83092705451833</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.55642036333573</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.31963755728034</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.53451788061989</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.98090217757456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.24864930132767</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.61767315543463</v>
+        <v>34.90040156827924</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.82125800179818</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.55953346519919</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.75506988081167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.86390298972456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.52766394359668</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.56019812969662</v>
       </c>
     </row>
   </sheetData>
@@ -12142,25 +12142,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.25093380342184</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.10942055925563</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.68920748834985</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.18826285349283</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.37266749860087</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.04231240443887</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.63362808494212</v>
+        <v>32.62083061270282</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.24155271283293</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.38020364207623</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.30398415020367</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51.3160159646667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.26748605098196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.9477645593112</v>
       </c>
     </row>
   </sheetData>
@@ -12224,25 +12224,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.68697260920817</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.99463490368544</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.23014426570195</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.244513698786</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.21670504328004</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.66598818481459</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.08730962789748</v>
+        <v>33.43308997712292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.2024385414786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.5656814886198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.3185584154436</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.66306682773951</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.08778239515291</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.05211155734009</v>
       </c>
     </row>
   </sheetData>
@@ -12306,25 +12306,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.28489589044895</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.60822926012314</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.42230488842104</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.96093962197486</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.77091006015443</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.49621129111867</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.75276264540219</v>
+        <v>44.07895254541321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.93612889897527</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.35973429813619</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.38579800351747</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.31447070916609</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45.93458471871236</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.50608794818594</v>
       </c>
     </row>
   </sheetData>
@@ -12388,25 +12388,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.92209693372701</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.60249098892606</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.158780461844</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.78616947927136</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.32169225726255</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.62568671868764</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45.68628764819455</v>
+        <v>35.32082467869321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.81959290619624</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.76187062279718</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.46788413982113</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.85434045648798</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.55315440701655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.41181515866654</v>
       </c>
     </row>
   </sheetData>
@@ -12470,25 +12470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.03707884798446</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.16350000921353</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.57546118763572</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.16539703137197</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.17568328486052</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.72912052685744</v>
-      </c>
-      <c r="H2" t="n">
-        <v>30.70290528867881</v>
+        <v>37.17273912588691</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.58422756225582</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.87746246499012</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.34308117417806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.00758031426092</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.36404142042647</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.93269789972564</v>
       </c>
     </row>
   </sheetData>
@@ -12552,25 +12552,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.81064774948369</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.43797120191349</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.44844681406311</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.83351097291603</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.46178366314812</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.17550101036222</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.12566993335904</v>
+        <v>42.79526569855719</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.73812445988128</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.66520347773151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.4284033038382</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.04712224500463</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.52544399050771</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.01883708967885</v>
       </c>
     </row>
   </sheetData>
@@ -12634,25 +12634,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.19040401629281</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.52068639003809</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.78167718793326</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.41845840182367</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.9893629498785</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.11120520721273</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.5251433277153</v>
+        <v>24.95483160821539</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.9243498770637</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.40818035559607</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.21409129482537</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.65776527547796</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.7673145697699</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.18963101523133</v>
       </c>
     </row>
   </sheetData>
@@ -12716,25 +12716,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.81628429728976</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.07527369598621</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.07354011303089</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.80736986643778</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.35530526992434</v>
-      </c>
-      <c r="G2" t="n">
-        <v>50.64817984247433</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.01894180043804</v>
+        <v>33.90144635208075</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.07373055945358</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.00128254873116</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.60611213918053</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.37147944625706</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.47037908336307</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.15253370849707</v>
       </c>
     </row>
   </sheetData>
@@ -12798,25 +12798,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.62099114871528</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.99626334208186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.78295270932096</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.77845618267568</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.79859896805636</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.02491773594012</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.70234337148704</v>
+        <v>36.17150088538573</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.83968531304364</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.69738890645237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.36338136201267</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.81619860183353</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.14923230583978</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.47230942156057</v>
       </c>
     </row>
   </sheetData>
@@ -12880,25 +12880,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.75346576273002</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.33002364723306</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.78927005972816</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.50665733333065</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.38844644774242</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.44149293738489</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.19085803030502</v>
+        <v>36.91670382011824</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.6666226774432</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.60710425353163</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.45455833331894</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.49964652555665</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.10465866543395</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.17653731758814</v>
       </c>
     </row>
   </sheetData>
@@ -12962,25 +12962,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.96101224232253</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.5993097773344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.91773255329419</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.55266990050767</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.88371113306053</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.1873293678544</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.05088299852095</v>
+        <v>43.70499015435289</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.97772343819614</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.84427342038437</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.98829452048475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.61897372082517</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.75620263263844</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.73584406280306</v>
       </c>
     </row>
   </sheetData>
@@ -13044,25 +13044,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.41123424990295</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.39963473518786</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50.02713766711189</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.52995912635193</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.93040994122262</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.94872280148655</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.98292253956478</v>
+        <v>34.1026377318776</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.58652875984871</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.0879462964208</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.89924587737147</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.33821969826572</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.85919066806298</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.53167112215609</v>
       </c>
     </row>
   </sheetData>
@@ -13126,25 +13126,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.95650002987696</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.39235994528737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.2205668913412</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.02092881746104</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.03319633742236</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.06903590366551</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.99678629196931</v>
+        <v>34.6969695940714</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.75540515972558</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.35909291014602</v>
+      </c>
+      <c r="E2" t="n">
+        <v>56.60103152098995</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.91496246920843</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.01437226124801</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.86758981972176</v>
       </c>
     </row>
   </sheetData>
@@ -13208,25 +13208,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.11745208459252</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.92924508548644</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.98476318463391</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.93901795133382</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.89135229918098</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.70769837530423</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.17464573207457</v>
+        <v>31.11740488884384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.3714490743644</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.48156514817627</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.69452054835366</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.71747791981482</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.91619875507943</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.94041027144017</v>
       </c>
     </row>
   </sheetData>
@@ -13290,25 +13290,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.04382227311059</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.64280658083816</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.93091866421385</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.46982194477142</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.6876029775259</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.21265573985811</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34.78945617662748</v>
+        <v>39.68668238362358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.42281730111085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.9674382980027</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.88243000341423</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.28007869969193</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.66854734534394</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.14479856044227</v>
       </c>
     </row>
   </sheetData>
@@ -13372,25 +13372,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.44016594872337</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.92059871119511</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.21274880879912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.42641530055966</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.43881855702551</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.84648589067338</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.90418975634059</v>
+        <v>29.7150697123927</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.80013484400587</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.22728525801586</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.14449594843494</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.17255899878323</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.51850426065569</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.54717953946218</v>
       </c>
     </row>
   </sheetData>
@@ -13454,25 +13454,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.79744580140342</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.18242409240691</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.98326724702459</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.45649756392968</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.48788989275697</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.73261809504231</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.2941214128592</v>
+        <v>32.98032402073992</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.19702976384842</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.76129070333178</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.20066033303625</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.7620507112288</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.92392516423324</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.19760367099537</v>
       </c>
     </row>
   </sheetData>
@@ -13536,25 +13536,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.1427089961914</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.83865064288464</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.38661019971286</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.15249351914038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.87946077101783</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.44318940214342</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.03551216107252</v>
+        <v>46.81809977330821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.93585417042934</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.28373119097515</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.77230606115649</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.2975643888909</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.53601447490253</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.93975425446148</v>
       </c>
     </row>
   </sheetData>
@@ -13618,25 +13618,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.80172892036908</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.79533573197529</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.42274281855124</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.54858792045599</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.52483497032583</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.85134863166279</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50.49985950484569</v>
+        <v>26.60725637105478</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.51697269968982</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.75747965467165</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.30809030478157</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.34224290573346</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.02881189810405</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.92614771459236</v>
       </c>
     </row>
   </sheetData>
@@ -13700,25 +13700,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.87487052831089</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.85900753275096</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.62761363095608</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.81495508391588</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.07890571528505</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.75122127250455</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.30542581839764</v>
+        <v>52.54892909118851</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.43330239360272</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.31725657944297</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.99716091693841</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.4355809384201</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.82634206469184</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.75685056241056</v>
       </c>
     </row>
   </sheetData>
@@ -13782,25 +13782,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.19572647824528</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.04018793768294</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.09402158945478</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.77364975476973</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.50304950158287</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.75153731045811</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.45387271012078</v>
+        <v>27.48409471481229</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.97966062965354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.18486987947058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.85252363802611</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.74344853165918</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.34310324197379</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.12410545170965</v>
       </c>
     </row>
   </sheetData>
@@ -13864,25 +13864,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.43439230477855</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.31210993725175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.50598603904189</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.43042999884216</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.7794478949986</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.7133302061925</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.22173251972784</v>
+        <v>31.73691291784318</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.80871052248889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.41278230534071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.54807764270323</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.26554690476522</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.93004875881368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.11243405166208</v>
       </c>
     </row>
   </sheetData>
@@ -13946,25 +13946,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.07968323979726</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.22369057823691</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.31429117020649</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.32353267997385</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.97628301238353</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.47298667416514</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.64872441459411</v>
+        <v>29.18262174309588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.54167258805358</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.45159636307761</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.88058424474454</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.21897427916343</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.19132249318446</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.63860385619826</v>
       </c>
     </row>
   </sheetData>
@@ -14028,25 +14028,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.53392836359448</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.34900050848071</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.76300396487293</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.88692797647055</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.5571879592547</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.77343102649002</v>
-      </c>
-      <c r="H2" t="n">
-        <v>56.82465006922435</v>
+        <v>47.77578869084181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.58775253907697</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.84598312389149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.71109851954463</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.95506200189926</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.8215121869653</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.64300948743481</v>
       </c>
     </row>
   </sheetData>
@@ -14110,25 +14110,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.7849052030454</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.23329947267524</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.85312583419501</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.57906388299984</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.31224450911033</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.68590427494924</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.12450999850306</v>
+        <v>40.6545694766095</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.41503536102132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.43287842868547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.01239898450885</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.53303591764912</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.99168470542195</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.00944344535738</v>
       </c>
     </row>
   </sheetData>
@@ -14192,25 +14192,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.77294177910625</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.76719633783883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.30969497980724</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.17493323963449</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.34889147238133</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.06739306075688</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.92011987255192</v>
+        <v>33.41430047777622</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.55115032972229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.21295256221928</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.07225104301099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.91685502998175</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27.78894611444344</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.42229020650103</v>
       </c>
     </row>
   </sheetData>
@@ -14274,25 +14274,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.05196415094523</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.44645536512753</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.77274965398975</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.03865077757491</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.76158794389335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.78250661675471</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.45486830788006</v>
+        <v>30.37149323855868</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.91037831314058</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.15001652963158</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48.51605281753777</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.63426983430527</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.28923865789052</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.27896965739349</v>
       </c>
     </row>
   </sheetData>
@@ -14356,25 +14356,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.67415946366874</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.44125933487673</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.68518675345488</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.47047786149256</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.58571221133254</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.24071523948774</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.22161037391645</v>
+        <v>33.20879599680648</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.53031881047265</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.49954514382451</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.87889560417134</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.56281292179462</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.10265438260661</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.60694527735627</v>
       </c>
     </row>
   </sheetData>
@@ -14438,25 +14438,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.53861507123984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.30370296966375</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.11823051730436</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.03486729659583</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.3671919207263</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.81280712269674</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.00228422789478</v>
+        <v>35.33755207393196</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.42637867184802</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.51233625248873</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.85561931683948</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.82710488497086</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.57002478443793</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.42509204963373</v>
       </c>
     </row>
   </sheetData>
@@ -14520,25 +14520,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.05315618953991</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.80220226817678</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.12848223984935</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.15143484338734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.07553976085465</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41.2173020569355</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.97873161464855</v>
+        <v>38.08957352731252</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.87875884071049</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.37906717399002</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.02265101193366</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.64963027820777</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.12864261537494</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.63800886029024</v>
       </c>
     </row>
   </sheetData>
@@ -14602,25 +14602,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.00495031844121</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.1606041394808</v>
-      </c>
-      <c r="D2" t="n">
-        <v>55.07998405722814</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.92781551020076</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.42740170796993</v>
-      </c>
-      <c r="G2" t="n">
-        <v>46.39822148002548</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.28126089695107</v>
+        <v>47.45339223434062</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.4480552541448</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.15447160860141</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.06167775938231</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.37255648631982</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.42532606296454</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.86696937865184</v>
       </c>
     </row>
   </sheetData>
@@ -14684,25 +14684,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.095597225875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.48600438218469</v>
-      </c>
-      <c r="D2" t="n">
-        <v>46.03928340931311</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.83362684797</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.3044686943999</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.91167825118021</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.4067515579763</v>
+        <v>34.17795983171771</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.5390302221105</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.35542934554581</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.91700572442947</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.29622964374231</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.51947293188439</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.48550649604297</v>
       </c>
     </row>
   </sheetData>
@@ -14766,25 +14766,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.2831194733466</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.28574191705681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.39816700636902</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.20250252337853</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.58665873465259</v>
-      </c>
-      <c r="G2" t="n">
-        <v>59.69618174389834</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.23100721125547</v>
+        <v>38.37232075469552</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.27109563632643</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.68441085346071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.76139514972353</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.30980878491695</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.80919395047843</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.8974597997624</v>
       </c>
     </row>
   </sheetData>
@@ -14848,25 +14848,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.42748494235548</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.77325225903061</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.0577488748735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.7168782365188</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.59722888963686</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.94610970952662</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.08985965371116</v>
+        <v>36.79855598036102</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.29288105717167</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.83028614027623</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.8293551487065</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.81340777880344</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.37624455717364</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.86301841042771</v>
       </c>
     </row>
   </sheetData>
@@ -14930,25 +14930,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.95604576068946</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.7528682647032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.9847812764089</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.94938077401579</v>
-      </c>
-      <c r="F2" t="n">
-        <v>52.41620596729617</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.70732171509102</v>
-      </c>
-      <c r="H2" t="n">
-        <v>41.18830371881727</v>
+        <v>35.55869079447555</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.34163957398835</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.03281951348558</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.04762032477557</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.98257197947737</v>
+      </c>
+      <c r="G2" t="n">
+        <v>53.73930930295894</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41.08485092953684</v>
       </c>
     </row>
   </sheetData>
@@ -15012,25 +15012,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.18724207516637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.78231885528717</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.08212750132715</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.54139579503168</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.4366905358307</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.35896549668001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.4595922604427</v>
+        <v>39.11084891543108</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.49452577925494</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.52413654283628</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.66634996096375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54.37595318363853</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.92239418619026</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.32030410787372</v>
       </c>
     </row>
   </sheetData>
@@ -15094,25 +15094,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.12682779235103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.24436953965817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.66677447388719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.93323661240173</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.1852829306269</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.04846954804279</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.20235854778505</v>
+        <v>25.92663984979896</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.19988295970916</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.72446664072984</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.11069945818826</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.82214384917401</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.68770063869002</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25.67871039580023</v>
       </c>
     </row>
   </sheetData>
@@ -15176,25 +15176,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.26751228380749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.07892705726201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.79036501394746</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.87483621828428</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.30543256042635</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43.32676108259182</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.63406473079684</v>
+        <v>36.62835057296141</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.02843760646307</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.63678280298021</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.52220516471598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.81819166567048</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.01333628138107</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.14086160205712</v>
       </c>
     </row>
   </sheetData>
@@ -15258,25 +15258,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.13362622428481</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.26591939760316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>54.47209022251775</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.412986885641</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.22215974394456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.456430458586</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40.28037713096247</v>
+        <v>38.44369302008401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.30183619073437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.61458731788231</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.32435982770772</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.69443245564826</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.46815262222736</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.24278283357424</v>
       </c>
     </row>
   </sheetData>
@@ -15340,25 +15340,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.63094081339234</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.88794825699798</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.48045200073455</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.33451524372374</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.86879952214889</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.7363881571239</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.87639705622588</v>
+        <v>35.89944959333435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.26726778319861</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.57218233293279</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.40893969945643</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.33801819268812</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.64802232698409</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.10593657571259</v>
       </c>
     </row>
   </sheetData>
@@ -15422,25 +15422,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.60065432135416</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.32844895227803</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.608962736056</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.00191797254261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.9859856762742</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.44580106956185</v>
-      </c>
-      <c r="H2" t="n">
-        <v>37.43132064764099</v>
+        <v>37.73731845681334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.7678799138468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.91516682830526</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.87497656468523</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.47381149090702</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.37985288701368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.16565279533824</v>
       </c>
     </row>
   </sheetData>
@@ -15504,25 +15504,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.20990328341965</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.73797249439025</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.89527169083645</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.61898119203989</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.86264102025832</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.61056286615986</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.92727191803155</v>
+        <v>30.36290518780946</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.44575279518004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.11597209349959</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.10186305098215</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.24877869258634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.54732897311351</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30.69154655359827</v>
       </c>
     </row>
   </sheetData>
@@ -15586,25 +15586,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.33234870169601</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.77083854367418</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.15144868116364</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.2078685068892</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.31228639247287</v>
-      </c>
-      <c r="G2" t="n">
-        <v>37.6249265857488</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.85012836890878</v>
+        <v>39.31073497422412</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.10080857788761</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.24923699909967</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.97203378982135</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.50682851585218</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.96169506172536</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.6687255610625</v>
       </c>
     </row>
   </sheetData>
@@ -15668,25 +15668,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.83557277732329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.93415270624727</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.59418037709703</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.25092215997618</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.28253844462377</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38.52431380713625</v>
-      </c>
-      <c r="H2" t="n">
-        <v>18.74414908788368</v>
+        <v>50.49885534768901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.57363455596033</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.92910174263269</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.14440726184677</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.86165522604643</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.14936439295627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31.13585703427027</v>
       </c>
     </row>
   </sheetData>
@@ -15750,25 +15750,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.11275274179319</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.95938546875931</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.54723758374065</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.88858506301688</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.88342327722131</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42.4011033531368</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.17683873119291</v>
+        <v>39.01889506850898</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.80678755399515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.10874075609487</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.15340327993665</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.85527823586702</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23.42295241243301</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27.6132530189778</v>
       </c>
     </row>
   </sheetData>
@@ -15832,25 +15832,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.17684615094277</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.49511194901935</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.19781527128799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.18769722133295</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.16612575090025</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27.88206213437008</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26.2292333249127</v>
+        <v>38.56090367915586</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.61870779448407</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.22247408237482</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.54564365981803</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.37477832298585</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.38435705136752</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.37803648783691</v>
       </c>
     </row>
   </sheetData>
@@ -15914,25 +15914,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.45340954211228</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.14301302242716</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.06963498175745</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.19613859700186</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.41041090936229</v>
-      </c>
-      <c r="G2" t="n">
-        <v>31.39084964940509</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43.16583887489897</v>
+        <v>30.84916043442244</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.19748741546567</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.56742607221631</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.93546693391827</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.50398034336293</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.04747840153944</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.75232422960769</v>
       </c>
     </row>
   </sheetData>
@@ -15996,25 +15996,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.32643957835507</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.99067114585896</v>
-      </c>
-      <c r="D2" t="n">
-        <v>59.96006238521921</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.0247108721634</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.15690506703057</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30.0994493392265</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.74869292685461</v>
+        <v>38.00729534225474</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.02408460289388</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.78730594930187</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.81508907726267</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.67298644499674</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.95721057741321</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.67159341939943</v>
       </c>
     </row>
   </sheetData>
@@ -16078,25 +16078,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.75402111948076</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.22955032811971</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.18681738942816</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.22359204426575</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.23480121607326</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.26796989440653</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.96991661166302</v>
+        <v>32.33722848650775</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.39880365677912</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.03862753797151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.35835032268958</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.33328759864433</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.46309936840298</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.465139940221</v>
       </c>
     </row>
   </sheetData>
@@ -16160,25 +16160,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.56266314176564</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.99536920072079</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51.0530813273777</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.06924952032099</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.21222438680704</v>
-      </c>
-      <c r="G2" t="n">
-        <v>44.10461626620892</v>
-      </c>
-      <c r="H2" t="n">
-        <v>59.02226692647773</v>
+        <v>35.84328503877725</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.93859187251282</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.32444344025614</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.90322711249913</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.09839221295707</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.66097709610726</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.82138248585574</v>
       </c>
     </row>
   </sheetData>
@@ -16242,25 +16242,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.4941570849209</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.03933377014413</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.71228791776668</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.03918739445577</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.53200369759486</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.6541302003609</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.38219985054912</v>
+        <v>35.570156013807</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.75276360712749</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.55855611387972</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.51210297846306</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.05181759931396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.65691183745762</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.1685928453342</v>
       </c>
     </row>
   </sheetData>
@@ -16324,25 +16324,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.37309344492941</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.70088481793467</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.93277349023965</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.41013565718853</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.46560945077986</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35.94165472151576</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.20759301497044</v>
+        <v>30.8806945536865</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.96212821921625</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.01797702600096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.7245455000529</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.83347404432547</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.63742067392791</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38.11346223448221</v>
       </c>
     </row>
   </sheetData>
@@ -16406,25 +16406,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.27742450130976</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.65548207822533</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.98975209410101</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.72229271547462</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.78145263883101</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.92710664002358</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36.77794391870085</v>
+        <v>30.11643254319701</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.89812861500308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.57358521089998</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.60832564619334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.93808472496357</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.80008518160359</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.19927340727538</v>
       </c>
     </row>
   </sheetData>
@@ -16488,25 +16488,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.82348262187254</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.62324144288556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.33509689079947</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.20363985050092</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.71155300529397</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40.07463968646671</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.3165741232311</v>
+        <v>25.3545464783978</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.06765524548996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.88030817284001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.3127651431283</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.1807634764211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.21227363661065</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.68461853625027</v>
       </c>
     </row>
   </sheetData>
@@ -16570,25 +16570,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.1632824779271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.14445167275306</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.3712863025815</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.5652591259597</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.21261941030617</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.72412087520556</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.73676162936108</v>
+        <v>37.77121689274068</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.46234676465716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.181707970893</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.69258787833417</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.96950572419108</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.59291586020689</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.50628811112814</v>
       </c>
     </row>
   </sheetData>
@@ -16652,25 +16652,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.98806463571289</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56.23874321800311</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.00399027245226</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.90986499203613</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.66099596490213</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45.43368093553651</v>
-      </c>
-      <c r="H2" t="n">
-        <v>38.22670126498016</v>
+        <v>34.72377629626685</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48.31463699562345</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.64845970927464</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.13158782537633</v>
+      </c>
+      <c r="F2" t="n">
+        <v>55.72420765637661</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.70733948997145</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.75293460129421</v>
       </c>
     </row>
   </sheetData>
@@ -16734,25 +16734,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.80411207533495</v>
-      </c>
-      <c r="C2" t="n">
-        <v>62.60539084226507</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.17556584355822</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.65821001588959</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.78533606731356</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.89753506616034</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.99713743439421</v>
+        <v>37.30613783829114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.55831311554984</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.87641225558401</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.36101824870033</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.67535665556071</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50.0295936907272</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.09489898603331</v>
       </c>
     </row>
   </sheetData>
@@ -16816,25 +16816,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38788526624242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.7505881339655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.19897368630713</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.44156346333046</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.5757906150126</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.401277366958</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42.02650472902428</v>
+        <v>31.33815674802347</v>
+      </c>
+      <c r="C2" t="n">
+        <v>54.12382958982339</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.07794717492717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.73671483938289</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.96485717710912</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.68922128099162</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.0520779550214</v>
       </c>
     </row>
   </sheetData>
@@ -16898,25 +16898,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.8914970503492</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.57800557573172</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.78097172101142</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.90867143947852</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.38083028695762</v>
-      </c>
-      <c r="G2" t="n">
-        <v>32.68732905522052</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.37324338709795</v>
+        <v>34.96608473803619</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.35405663309787</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.1310781890656</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.07899104530114</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.78753985118598</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.78065635912952</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.03724554014462</v>
       </c>
     </row>
   </sheetData>
@@ -16980,25 +16980,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.17539329269017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.16180922713888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.42477308085368</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.4925359333052</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.88323551759484</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33.06957105900491</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.43352906107574</v>
+        <v>25.38021383732347</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.84633277587492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.22268826480941</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.39709430311954</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.00447136678374</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.7484545477085</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.68493128249166</v>
       </c>
     </row>
   </sheetData>
